--- a/Water Disposal History.xlsx
+++ b/Water Disposal History.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://etswdmail-my.sharepoint.com/personal/lfrideley_etswd_com/Documents/Documents/SARIMA Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{9F342BE3-2F2B-4A33-86FA-5252C47A49C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B02B1C-EB14-491F-A3C1-53E1A66218A5}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{9F342BE3-2F2B-4A33-86FA-5252C47A49C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0786317-38BA-4F04-AA8F-45FD45D92FC4}"/>
   <bookViews>
     <workbookView xWindow="32175" yWindow="1530" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{85408E0C-C59E-4CA0-92DA-6AA07159AB49}"/>
   </bookViews>
@@ -126,16 +126,16 @@
     <t>BASA Total Allocated Volume</t>
   </si>
   <si>
-    <t>Total Water Volume</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
     <t>Diff</t>
   </si>
   <si>
-    <t>Forward-Backward Average</t>
+    <t>Forward - Backword average</t>
+  </si>
+  <si>
+    <t>Total Water Volume 1</t>
   </si>
 </sst>
 </file>
@@ -48315,12 +48315,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62516834-FDAB-45A0-893B-2B6358A8E52F}">
-  <dimension ref="A1:D344"/>
+  <dimension ref="A1:D428"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="29" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -48328,5508 +48327,5774 @@
         <v>28</v>
       </c>
       <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="D1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
+        <v>35796</v>
+      </c>
+      <c r="B2" s="4">
         <v>33775964</v>
       </c>
-      <c r="B2" s="3">
-        <v>35796</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
+        <v>35827</v>
+      </c>
+      <c r="B3" s="4">
         <v>30600608</v>
       </c>
-      <c r="B3" s="3">
-        <v>35827</v>
-      </c>
       <c r="C3" s="29">
-        <f>A3-A2</f>
+        <f>B3-B2</f>
         <v>-3175356</v>
       </c>
-      <c r="D3" s="4">
-        <f>(A2+A4)/2</f>
+      <c r="D3">
+        <f>(B2+B4)/2</f>
         <v>33721885.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
+        <v>35855</v>
+      </c>
+      <c r="B4" s="4">
         <v>33667807</v>
       </c>
-      <c r="B4" s="3">
-        <v>35855</v>
-      </c>
       <c r="C4" s="29">
-        <f t="shared" ref="C4:C67" si="0">A4-A3</f>
+        <f t="shared" ref="C4:C67" si="0">B4-B3</f>
         <v>3067199</v>
       </c>
-      <c r="D4" s="4">
-        <f t="shared" ref="D4:D67" si="1">(A3+A5)/2</f>
+      <c r="D4">
+        <f t="shared" ref="D4:D67" si="1">(B3+B5)/2</f>
         <v>31181405</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
+        <v>35886</v>
+      </c>
+      <c r="B5" s="4">
         <v>31762202</v>
-      </c>
-      <c r="B5" s="3">
-        <v>35886</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
         <v>-1905605</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <f t="shared" si="1"/>
         <v>33083817.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
+        <v>35916</v>
+      </c>
+      <c r="B6" s="4">
         <v>32499828</v>
-      </c>
-      <c r="B6" s="3">
-        <v>35916</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
         <v>737626</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <f t="shared" si="1"/>
         <v>31276953.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
+        <v>35947</v>
+      </c>
+      <c r="B7" s="4">
         <v>30791705</v>
-      </c>
-      <c r="B7" s="3">
-        <v>35947</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
         <v>-1708123</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <f t="shared" si="1"/>
         <v>31833535.5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
+        <v>35977</v>
+      </c>
+      <c r="B8" s="4">
         <v>31167243</v>
-      </c>
-      <c r="B8" s="3">
-        <v>35977</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>375538</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <f t="shared" si="1"/>
         <v>30624828</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
+        <v>36008</v>
+      </c>
+      <c r="B9" s="4">
         <v>30457951</v>
-      </c>
-      <c r="B9" s="3">
-        <v>36008</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>-709292</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9">
         <f t="shared" si="1"/>
         <v>30066511.5</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
+        <v>36039</v>
+      </c>
+      <c r="B10" s="4">
         <v>28965780</v>
-      </c>
-      <c r="B10" s="3">
-        <v>36039</v>
       </c>
       <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>-1492171</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10">
         <f t="shared" si="1"/>
         <v>30209072.5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
+        <v>36069</v>
+      </c>
+      <c r="B11" s="4">
         <v>29960194</v>
-      </c>
-      <c r="B11" s="3">
-        <v>36069</v>
       </c>
       <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>994414</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11">
         <f t="shared" si="1"/>
         <v>28534857.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
+        <v>36100</v>
+      </c>
+      <c r="B12" s="4">
         <v>28103935</v>
-      </c>
-      <c r="B12" s="3">
-        <v>36100</v>
       </c>
       <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>-1856259</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12">
         <f t="shared" si="1"/>
         <v>28897874.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
+        <v>36130</v>
+      </c>
+      <c r="B13" s="4">
         <v>27835555</v>
-      </c>
-      <c r="B13" s="3">
-        <v>36130</v>
       </c>
       <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>-268380</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13">
         <f t="shared" si="1"/>
         <v>27652255.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
+        <v>36161</v>
+      </c>
+      <c r="B14" s="4">
         <v>27200576</v>
-      </c>
-      <c r="B14" s="3">
-        <v>36161</v>
       </c>
       <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>-634979</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14">
         <f t="shared" si="1"/>
-        <v>26308728.5</v>
+        <v>27440151.5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>24781902</v>
-      </c>
-      <c r="B15" s="3">
+      <c r="A15" s="3">
         <v>36192</v>
+      </c>
+      <c r="B15" s="4">
+        <v>27044748</v>
       </c>
       <c r="C15" s="29">
         <f t="shared" si="0"/>
-        <v>-2418674</v>
-      </c>
-      <c r="D15" s="4">
+        <v>-155828</v>
+      </c>
+      <c r="D15">
         <f t="shared" si="1"/>
         <v>27044747.5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
+        <v>36220</v>
+      </c>
+      <c r="B16" s="4">
         <v>26888919</v>
-      </c>
-      <c r="B16" s="3">
-        <v>36220</v>
       </c>
       <c r="C16" s="29">
         <f t="shared" si="0"/>
-        <v>2107017</v>
-      </c>
-      <c r="D16" s="4">
+        <v>-155829</v>
+      </c>
+      <c r="D16">
         <f t="shared" si="1"/>
-        <v>25338833.5</v>
+        <v>26470256.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
+        <v>36251</v>
+      </c>
+      <c r="B17" s="4">
         <v>25895765</v>
-      </c>
-      <c r="B17" s="3">
-        <v>36251</v>
       </c>
       <c r="C17" s="29">
         <f t="shared" si="0"/>
         <v>-993154</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <f t="shared" si="1"/>
         <v>27015334.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
+        <v>36281</v>
+      </c>
+      <c r="B18" s="4">
         <v>27141750</v>
-      </c>
-      <c r="B18" s="3">
-        <v>36281</v>
       </c>
       <c r="C18" s="29">
         <f t="shared" si="0"/>
         <v>1245985</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18">
         <f t="shared" si="1"/>
         <v>26269555</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
+        <v>36312</v>
+      </c>
+      <c r="B19" s="4">
         <v>26643345</v>
-      </c>
-      <c r="B19" s="3">
-        <v>36312</v>
       </c>
       <c r="C19" s="29">
         <f t="shared" si="0"/>
         <v>-498405</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19">
         <f t="shared" si="1"/>
         <v>27362538.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
+        <v>36342</v>
+      </c>
+      <c r="B20" s="4">
         <v>27583327</v>
-      </c>
-      <c r="B20" s="3">
-        <v>36342</v>
       </c>
       <c r="C20" s="29">
         <f t="shared" si="0"/>
         <v>939982</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20">
         <f t="shared" si="1"/>
         <v>27393899.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
+        <v>36373</v>
+      </c>
+      <c r="B21" s="4">
         <v>28144454</v>
-      </c>
-      <c r="B21" s="3">
-        <v>36373</v>
       </c>
       <c r="C21" s="29">
         <f t="shared" si="0"/>
         <v>561127</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21">
         <f t="shared" si="1"/>
         <v>27643033</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
+        <v>36404</v>
+      </c>
+      <c r="B22" s="4">
         <v>27702739</v>
-      </c>
-      <c r="B22" s="3">
-        <v>36404</v>
       </c>
       <c r="C22" s="29">
         <f t="shared" si="0"/>
         <v>-441715</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22">
         <f t="shared" si="1"/>
         <v>28422791.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
+        <v>36434</v>
+      </c>
+      <c r="B23" s="4">
         <v>28701129</v>
-      </c>
-      <c r="B23" s="3">
-        <v>36434</v>
       </c>
       <c r="C23" s="29">
         <f t="shared" si="0"/>
         <v>998390</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23">
         <f t="shared" si="1"/>
         <v>27600989.5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
+        <v>36465</v>
+      </c>
+      <c r="B24" s="4">
         <v>27499240</v>
-      </c>
-      <c r="B24" s="3">
-        <v>36465</v>
       </c>
       <c r="C24" s="29">
         <f t="shared" si="0"/>
         <v>-1201889</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24">
         <f t="shared" si="1"/>
         <v>28661655</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
+        <v>36495</v>
+      </c>
+      <c r="B25" s="4">
         <v>28622181</v>
-      </c>
-      <c r="B25" s="3">
-        <v>36495</v>
       </c>
       <c r="C25" s="29">
         <f t="shared" si="0"/>
         <v>1122941</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25">
         <f t="shared" si="1"/>
         <v>28159483.5</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
+        <v>36526</v>
+      </c>
+      <c r="B26" s="4">
         <v>28819727</v>
-      </c>
-      <c r="B26" s="3">
-        <v>36526</v>
       </c>
       <c r="C26" s="29">
         <f t="shared" si="0"/>
         <v>197546</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26">
         <f t="shared" si="1"/>
         <v>28137444</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
+        <v>36557</v>
+      </c>
+      <c r="B27" s="4">
         <v>27652707</v>
-      </c>
-      <c r="B27" s="3">
-        <v>36557</v>
       </c>
       <c r="C27" s="29">
         <f t="shared" si="0"/>
         <v>-1167020</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27">
         <f t="shared" si="1"/>
         <v>29457736</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
+        <v>36586</v>
+      </c>
+      <c r="B28" s="4">
         <v>30095745</v>
-      </c>
-      <c r="B28" s="3">
-        <v>36586</v>
       </c>
       <c r="C28" s="29">
         <f t="shared" si="0"/>
         <v>2443038</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28">
         <f t="shared" si="1"/>
         <v>28678657.5</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
+        <v>36617</v>
+      </c>
+      <c r="B29" s="4">
         <v>29704608</v>
-      </c>
-      <c r="B29" s="3">
-        <v>36617</v>
       </c>
       <c r="C29" s="29">
         <f t="shared" si="0"/>
         <v>-391137</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29">
         <f t="shared" si="1"/>
         <v>30003355.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
+        <v>36647</v>
+      </c>
+      <c r="B30" s="4">
         <v>29910966</v>
-      </c>
-      <c r="B30" s="3">
-        <v>36647</v>
       </c>
       <c r="C30" s="29">
         <f t="shared" si="0"/>
         <v>206358</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30">
         <f t="shared" si="1"/>
         <v>29512617</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
+        <v>36678</v>
+      </c>
+      <c r="B31" s="4">
         <v>29320626</v>
-      </c>
-      <c r="B31" s="3">
-        <v>36678</v>
       </c>
       <c r="C31" s="29">
         <f t="shared" si="0"/>
         <v>-590340</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31">
         <f t="shared" si="1"/>
         <v>30214554</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
+        <v>36708</v>
+      </c>
+      <c r="B32" s="4">
         <v>30518142</v>
-      </c>
-      <c r="B32" s="3">
-        <v>36708</v>
       </c>
       <c r="C32" s="29">
         <f t="shared" si="0"/>
         <v>1197516</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32">
         <f t="shared" si="1"/>
         <v>30010301</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
+        <v>36739</v>
+      </c>
+      <c r="B33" s="4">
         <v>30699976</v>
-      </c>
-      <c r="B33" s="3">
-        <v>36739</v>
       </c>
       <c r="C33" s="29">
         <f t="shared" si="0"/>
         <v>181834</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33">
         <f t="shared" si="1"/>
         <v>29981839.5</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
+        <v>36770</v>
+      </c>
+      <c r="B34" s="4">
         <v>29445537</v>
-      </c>
-      <c r="B34" s="3">
-        <v>36770</v>
       </c>
       <c r="C34" s="29">
         <f t="shared" si="0"/>
         <v>-1254439</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34">
         <f t="shared" si="1"/>
         <v>30674473.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
+        <v>36800</v>
+      </c>
+      <c r="B35" s="4">
         <v>30648971</v>
-      </c>
-      <c r="B35" s="3">
-        <v>36800</v>
       </c>
       <c r="C35" s="29">
         <f t="shared" si="0"/>
         <v>1203434</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35">
         <f t="shared" si="1"/>
         <v>29416862</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+      <c r="A36" s="3">
+        <v>36831</v>
+      </c>
+      <c r="B36" s="4">
         <v>29388187</v>
-      </c>
-      <c r="B36" s="3">
-        <v>36831</v>
       </c>
       <c r="C36" s="29">
         <f t="shared" si="0"/>
         <v>-1260784</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36">
         <f t="shared" si="1"/>
         <v>29793385</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <f>D37</f>
+      <c r="A37" s="3">
+        <v>36861</v>
+      </c>
+      <c r="B37" s="4">
         <v>28937799</v>
       </c>
-      <c r="B37" s="3">
-        <v>36861</v>
-      </c>
-      <c r="D37" s="4">
+      <c r="C37" s="29">
+        <f t="shared" si="0"/>
+        <v>-450388</v>
+      </c>
+      <c r="D37">
         <f t="shared" si="1"/>
         <v>28937799</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
+        <v>36892</v>
+      </c>
+      <c r="B38" s="4">
         <v>28487411</v>
-      </c>
-      <c r="B38" s="3">
-        <v>36892</v>
       </c>
       <c r="C38" s="29">
         <f t="shared" si="0"/>
         <v>-450388</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38">
         <f t="shared" si="1"/>
         <v>27870780.5</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+      <c r="A39" s="3">
+        <v>36923</v>
+      </c>
+      <c r="B39" s="4">
         <v>26803762</v>
-      </c>
-      <c r="B39" s="3">
-        <v>36923</v>
       </c>
       <c r="C39" s="29">
         <f t="shared" si="0"/>
         <v>-1683649</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39">
         <f t="shared" si="1"/>
         <v>28994175.5</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+      <c r="A40" s="3">
+        <v>36951</v>
+      </c>
+      <c r="B40" s="4">
         <v>29500940</v>
-      </c>
-      <c r="B40" s="3">
-        <v>36951</v>
       </c>
       <c r="C40" s="29">
         <f t="shared" si="0"/>
         <v>2697178</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40">
         <f t="shared" si="1"/>
         <v>27981758.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+      <c r="A41" s="3">
+        <v>36982</v>
+      </c>
+      <c r="B41" s="4">
         <v>29159755</v>
-      </c>
-      <c r="B41" s="3">
-        <v>36982</v>
       </c>
       <c r="C41" s="29">
         <f t="shared" si="0"/>
         <v>-341185</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41">
         <f t="shared" si="1"/>
         <v>29888267</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="A42" s="3">
+        <v>37012</v>
+      </c>
+      <c r="B42" s="4">
         <v>30275594</v>
-      </c>
-      <c r="B42" s="3">
-        <v>37012</v>
       </c>
       <c r="C42" s="29">
         <f t="shared" si="0"/>
         <v>1115839</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42">
         <f t="shared" si="1"/>
         <v>29187010.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+      <c r="A43" s="3">
+        <v>37043</v>
+      </c>
+      <c r="B43" s="4">
         <v>29214266</v>
-      </c>
-      <c r="B43" s="3">
-        <v>37043</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="0"/>
         <v>-1061328</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43">
         <f t="shared" si="1"/>
         <v>30448845</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
+        <v>37073</v>
+      </c>
+      <c r="B44" s="4">
         <v>30622096</v>
-      </c>
-      <c r="B44" s="3">
-        <v>37073</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="0"/>
         <v>1407830</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44">
         <f t="shared" si="1"/>
         <v>30022938.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+      <c r="A45" s="3">
+        <v>37104</v>
+      </c>
+      <c r="B45" s="4">
         <v>30831611</v>
-      </c>
-      <c r="B45" s="3">
-        <v>37104</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="0"/>
         <v>209515</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45">
         <f t="shared" si="1"/>
         <v>30032879.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
+        <v>37135</v>
+      </c>
+      <c r="B46" s="4">
         <v>29443663</v>
-      </c>
-      <c r="B46" s="3">
-        <v>37135</v>
       </c>
       <c r="C46" s="29">
         <f t="shared" si="0"/>
         <v>-1387948</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46">
         <f t="shared" si="1"/>
         <v>30950444</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+      <c r="A47" s="3">
+        <v>37165</v>
+      </c>
+      <c r="B47" s="4">
         <v>31069277</v>
-      </c>
-      <c r="B47" s="3">
-        <v>37165</v>
       </c>
       <c r="C47" s="29">
         <f t="shared" si="0"/>
         <v>1625614</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47">
         <f t="shared" si="1"/>
         <v>29640681.5</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
+        <v>37196</v>
+      </c>
+      <c r="B48" s="4">
         <v>29837700</v>
-      </c>
-      <c r="B48" s="3">
-        <v>37196</v>
       </c>
       <c r="C48" s="29">
         <f t="shared" si="0"/>
         <v>-1231577</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48">
         <f t="shared" si="1"/>
         <v>30907257</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+      <c r="A49" s="3">
+        <v>37226</v>
+      </c>
+      <c r="B49" s="4">
         <v>30745237</v>
-      </c>
-      <c r="B49" s="3">
-        <v>37226</v>
       </c>
       <c r="C49" s="29">
         <f t="shared" si="0"/>
         <v>907537</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49">
         <f t="shared" si="1"/>
         <v>30062332</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
+        <v>37257</v>
+      </c>
+      <c r="B50" s="4">
         <v>30286964</v>
-      </c>
-      <c r="B50" s="3">
-        <v>37257</v>
       </c>
       <c r="C50" s="29">
         <f t="shared" si="0"/>
         <v>-458273</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50">
         <f t="shared" si="1"/>
-        <v>29117079</v>
+        <v>30583756.5</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
-        <v>27488921</v>
-      </c>
-      <c r="B51" s="3">
+      <c r="A51" s="3">
         <v>37288</v>
+      </c>
+      <c r="B51" s="4">
+        <v>30422276</v>
       </c>
       <c r="C51" s="29">
         <f t="shared" si="0"/>
-        <v>-2798043</v>
-      </c>
-      <c r="D51" s="4">
+        <v>135312</v>
+      </c>
+      <c r="D51">
         <f t="shared" si="1"/>
         <v>30422275.5</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+      <c r="A52" s="3">
+        <v>37316</v>
+      </c>
+      <c r="B52" s="4">
         <v>30557587</v>
-      </c>
-      <c r="B52" s="3">
-        <v>37316</v>
       </c>
       <c r="C52" s="29">
         <f t="shared" si="0"/>
-        <v>3068666</v>
-      </c>
-      <c r="D52" s="4">
+        <v>135311</v>
+      </c>
+      <c r="D52">
         <f t="shared" si="1"/>
-        <v>28411734</v>
+        <v>29878411.5</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+      <c r="A53" s="3">
+        <v>37347</v>
+      </c>
+      <c r="B53" s="4">
         <v>29334547</v>
-      </c>
-      <c r="B53" s="3">
-        <v>37347</v>
       </c>
       <c r="C53" s="29">
         <f t="shared" si="0"/>
         <v>-1223040</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53">
         <f t="shared" si="1"/>
         <v>30393210.5</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="A54" s="3">
+        <v>37377</v>
+      </c>
+      <c r="B54" s="4">
         <v>30228834</v>
-      </c>
-      <c r="B54" s="3">
-        <v>37377</v>
       </c>
       <c r="C54" s="29">
         <f t="shared" si="0"/>
         <v>894287</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54">
         <f t="shared" si="1"/>
         <v>29205223.5</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+      <c r="A55" s="3">
+        <v>37408</v>
+      </c>
+      <c r="B55" s="4">
         <v>29075900</v>
-      </c>
-      <c r="B55" s="3">
-        <v>37408</v>
       </c>
       <c r="C55" s="29">
         <f t="shared" si="0"/>
         <v>-1152934</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55">
         <f t="shared" si="1"/>
         <v>30149097</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+      <c r="A56" s="3">
+        <v>37438</v>
+      </c>
+      <c r="B56" s="4">
         <v>30069360</v>
-      </c>
-      <c r="B56" s="3">
-        <v>37438</v>
       </c>
       <c r="C56" s="29">
         <f t="shared" si="0"/>
         <v>993460</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56">
         <f t="shared" si="1"/>
         <v>29486452</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="4">
+      <c r="A57" s="3">
+        <v>37469</v>
+      </c>
+      <c r="B57" s="4">
         <v>29897004</v>
-      </c>
-      <c r="B57" s="3">
-        <v>37469</v>
       </c>
       <c r="C57" s="29">
         <f t="shared" si="0"/>
         <v>-172356</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57">
         <f t="shared" si="1"/>
         <v>29670808</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
+      <c r="A58" s="3">
+        <v>37500</v>
+      </c>
+      <c r="B58" s="4">
         <v>29272256</v>
-      </c>
-      <c r="B58" s="3">
-        <v>37500</v>
       </c>
       <c r="C58" s="29">
         <f t="shared" si="0"/>
         <v>-624748</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58">
         <f t="shared" si="1"/>
         <v>30058354</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="4">
+      <c r="A59" s="3">
+        <v>37530</v>
+      </c>
+      <c r="B59" s="4">
         <v>30219704</v>
-      </c>
-      <c r="B59" s="3">
-        <v>37530</v>
       </c>
       <c r="C59" s="29">
         <f t="shared" si="0"/>
         <v>947448</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59">
         <f t="shared" si="1"/>
         <v>29194679.5</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
+      <c r="A60" s="3">
+        <v>37561</v>
+      </c>
+      <c r="B60" s="4">
         <v>29117103</v>
-      </c>
-      <c r="B60" s="3">
-        <v>37561</v>
       </c>
       <c r="C60" s="29">
         <f t="shared" si="0"/>
         <v>-1102601</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60">
         <f t="shared" si="1"/>
         <v>30013149.5</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
+      <c r="A61" s="3">
+        <v>37591</v>
+      </c>
+      <c r="B61" s="4">
         <v>29806595</v>
-      </c>
-      <c r="B61" s="3">
-        <v>37591</v>
       </c>
       <c r="C61" s="29">
         <f t="shared" si="0"/>
         <v>689492</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61">
         <f t="shared" si="1"/>
         <v>29391776.5</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
+      <c r="A62" s="3">
+        <v>37622</v>
+      </c>
+      <c r="B62" s="4">
         <v>29666450</v>
-      </c>
-      <c r="B62" s="3">
-        <v>37622</v>
       </c>
       <c r="C62" s="29">
         <f t="shared" si="0"/>
         <v>-140145</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62">
         <f t="shared" si="1"/>
-        <v>28506796.5</v>
+        <v>29844533.5</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
-        <v>27206998</v>
-      </c>
-      <c r="B63" s="3">
+      <c r="A63" s="3">
         <v>37653</v>
+      </c>
+      <c r="B63" s="4">
+        <v>29882472</v>
       </c>
       <c r="C63" s="29">
         <f t="shared" si="0"/>
-        <v>-2459452</v>
-      </c>
-      <c r="D63" s="4">
+        <v>216022</v>
+      </c>
+      <c r="D63">
         <f t="shared" si="1"/>
         <v>29882471.5</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
+      <c r="A64" s="3">
+        <v>37681</v>
+      </c>
+      <c r="B64" s="4">
         <v>30098493</v>
-      </c>
-      <c r="B64" s="3">
-        <v>37681</v>
       </c>
       <c r="C64" s="29">
         <f t="shared" si="0"/>
-        <v>2891495</v>
-      </c>
-      <c r="D64" s="4">
+        <v>216021</v>
+      </c>
+      <c r="D64">
         <f t="shared" si="1"/>
-        <v>28020144</v>
+        <v>29357881</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
+      <c r="A65" s="3">
+        <v>37712</v>
+      </c>
+      <c r="B65" s="4">
         <v>28833290</v>
-      </c>
-      <c r="B65" s="3">
-        <v>37712</v>
       </c>
       <c r="C65" s="29">
         <f t="shared" si="0"/>
         <v>-1265203</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65">
         <f t="shared" si="1"/>
         <v>29872549.5</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
+      <c r="A66" s="3">
+        <v>37742</v>
+      </c>
+      <c r="B66" s="4">
         <v>29646606</v>
-      </c>
-      <c r="B66" s="3">
-        <v>37742</v>
       </c>
       <c r="C66" s="29">
         <f t="shared" si="0"/>
         <v>813316</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66">
         <f t="shared" si="1"/>
         <v>28596848.5</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="4">
+      <c r="A67" s="3">
+        <v>37773</v>
+      </c>
+      <c r="B67" s="4">
         <v>28360407</v>
-      </c>
-      <c r="B67" s="3">
-        <v>37773</v>
       </c>
       <c r="C67" s="29">
         <f t="shared" si="0"/>
         <v>-1286199</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67">
         <f t="shared" si="1"/>
         <v>29424111</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="4">
+      <c r="A68" s="3">
+        <v>37803</v>
+      </c>
+      <c r="B68" s="4">
         <v>29201616</v>
       </c>
-      <c r="B68" s="3">
-        <v>37803</v>
-      </c>
       <c r="C68" s="29">
-        <f t="shared" ref="C68:C131" si="2">A68-A67</f>
+        <f t="shared" ref="C68:C131" si="2">B68-B67</f>
         <v>841209</v>
       </c>
-      <c r="D68" s="4">
-        <f t="shared" ref="D68:D131" si="3">(A67+A69)/2</f>
+      <c r="D68">
+        <f t="shared" ref="D68:D131" si="3">(B67+B69)/2</f>
         <v>28686613.5</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="4">
+      <c r="A69" s="3">
+        <v>37834</v>
+      </c>
+      <c r="B69" s="4">
         <v>29012820</v>
-      </c>
-      <c r="B69" s="3">
-        <v>37834</v>
       </c>
       <c r="C69" s="29">
         <f t="shared" si="2"/>
         <v>-188796</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69">
         <f t="shared" si="3"/>
         <v>28776014</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4">
+      <c r="A70" s="3">
+        <v>37865</v>
+      </c>
+      <c r="B70" s="4">
         <v>28350412</v>
-      </c>
-      <c r="B70" s="3">
-        <v>37865</v>
       </c>
       <c r="C70" s="29">
         <f t="shared" si="2"/>
         <v>-662408</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70">
         <f t="shared" si="3"/>
         <v>29105307</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="4">
+      <c r="A71" s="3">
+        <v>37895</v>
+      </c>
+      <c r="B71" s="4">
         <v>29197794</v>
-      </c>
-      <c r="B71" s="3">
-        <v>37895</v>
       </c>
       <c r="C71" s="29">
         <f t="shared" si="2"/>
         <v>847382</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71">
         <f t="shared" si="3"/>
         <v>28236620.5</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4">
+      <c r="A72" s="3">
+        <v>37926</v>
+      </c>
+      <c r="B72" s="4">
         <v>28122829</v>
-      </c>
-      <c r="B72" s="3">
-        <v>37926</v>
       </c>
       <c r="C72" s="29">
         <f t="shared" si="2"/>
         <v>-1074965</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72">
         <f t="shared" si="3"/>
         <v>28890410.5</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="4">
+      <c r="A73" s="3">
+        <v>37956</v>
+      </c>
+      <c r="B73" s="4">
         <v>28583027</v>
-      </c>
-      <c r="B73" s="3">
-        <v>37956</v>
       </c>
       <c r="C73" s="29">
         <f t="shared" si="2"/>
         <v>460198</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73">
         <f t="shared" si="3"/>
         <v>28410885</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
+      <c r="A74" s="3">
+        <v>37987</v>
+      </c>
+      <c r="B74" s="4">
         <v>28698941</v>
-      </c>
-      <c r="B74" s="3">
-        <v>37987</v>
       </c>
       <c r="C74" s="29">
         <f t="shared" si="2"/>
         <v>115914</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74">
         <f t="shared" si="3"/>
         <v>27920493</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4">
+      <c r="A75" s="3">
+        <v>38018</v>
+      </c>
+      <c r="B75" s="4">
         <v>27257959</v>
-      </c>
-      <c r="B75" s="3">
-        <v>38018</v>
       </c>
       <c r="C75" s="29">
         <f t="shared" si="2"/>
         <v>-1440982</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75">
         <f t="shared" si="3"/>
         <v>28821399.5</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="8">
+      <c r="A76" s="3">
+        <v>38047</v>
+      </c>
+      <c r="B76" s="8">
         <v>28943858</v>
-      </c>
-      <c r="B76" s="3">
-        <v>38047</v>
       </c>
       <c r="C76" s="29">
         <f t="shared" si="2"/>
         <v>1685899</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76">
         <f t="shared" si="3"/>
         <v>27644124.5</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="8">
+      <c r="A77" s="3">
+        <v>38078</v>
+      </c>
+      <c r="B77" s="8">
         <v>28030290</v>
-      </c>
-      <c r="B77" s="3">
-        <v>38078</v>
       </c>
       <c r="C77" s="29">
         <f t="shared" si="2"/>
         <v>-913568</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77">
         <f t="shared" si="3"/>
         <v>28900747</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
+      <c r="A78" s="3">
+        <v>38108</v>
+      </c>
+      <c r="B78" s="8">
         <v>28857636</v>
-      </c>
-      <c r="B78" s="3">
-        <v>38108</v>
       </c>
       <c r="C78" s="29">
         <f t="shared" si="2"/>
         <v>827346</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78">
         <f t="shared" si="3"/>
-        <v>28428774.25</v>
+        <v>28428774.5</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="8">
-        <f>D79</f>
-        <v>28827258.5</v>
-      </c>
-      <c r="B79" s="3">
+      <c r="A79" s="3">
         <v>38139</v>
       </c>
+      <c r="B79" s="8">
+        <v>28827259</v>
+      </c>
       <c r="C79" s="29">
-        <f>D79</f>
-        <v>28827258.5</v>
-      </c>
-      <c r="D79" s="4">
+        <f t="shared" si="2"/>
+        <v>-30377</v>
+      </c>
+      <c r="D79">
         <f t="shared" si="3"/>
         <v>28827258.5</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
+      <c r="A80" s="3">
+        <v>38169</v>
+      </c>
+      <c r="B80" s="8">
         <v>28796881</v>
-      </c>
-      <c r="B80" s="3">
-        <v>38169</v>
       </c>
       <c r="C80" s="29">
         <f t="shared" si="2"/>
-        <v>-30377.5</v>
-      </c>
-      <c r="D80" s="4">
+        <v>-30378</v>
+      </c>
+      <c r="D80">
         <f t="shared" si="3"/>
-        <v>28600616.25</v>
+        <v>28600616.5</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="8">
+      <c r="A81" s="3">
+        <v>38200</v>
+      </c>
+      <c r="B81" s="8">
         <v>28373974</v>
-      </c>
-      <c r="B81" s="3">
-        <v>38200</v>
       </c>
       <c r="C81" s="29">
         <f t="shared" si="2"/>
         <v>-422907</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81">
         <f t="shared" si="3"/>
         <v>28212129.5</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
+      <c r="A82" s="3">
+        <v>38231</v>
+      </c>
+      <c r="B82" s="8">
         <v>27627378</v>
-      </c>
-      <c r="B82" s="3">
-        <v>38231</v>
       </c>
       <c r="C82" s="29">
         <f t="shared" si="2"/>
         <v>-746596</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82">
         <f t="shared" si="3"/>
         <v>28637041.5</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="8">
+      <c r="A83" s="3">
+        <v>38261</v>
+      </c>
+      <c r="B83" s="8">
         <v>28900109</v>
-      </c>
-      <c r="B83" s="3">
-        <v>38261</v>
       </c>
       <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>1272731</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83">
         <f t="shared" si="3"/>
         <v>27812998</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="8">
+      <c r="A84" s="3">
+        <v>38292</v>
+      </c>
+      <c r="B84" s="8">
         <v>27998618</v>
-      </c>
-      <c r="B84" s="3">
-        <v>38292</v>
       </c>
       <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>-901491</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84">
         <f t="shared" si="3"/>
         <v>28599390</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="8">
+      <c r="A85" s="3">
+        <v>38322</v>
+      </c>
+      <c r="B85" s="8">
         <v>28298671</v>
-      </c>
-      <c r="B85" s="3">
-        <v>38322</v>
       </c>
       <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>300053</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85">
         <f t="shared" si="3"/>
         <v>28196296</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="8">
+      <c r="A86" s="3">
+        <v>38353</v>
+      </c>
+      <c r="B86" s="8">
         <v>28393974</v>
-      </c>
-      <c r="B86" s="3">
-        <v>38353</v>
       </c>
       <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>95303</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86">
         <f t="shared" si="3"/>
-        <v>28533074.25</v>
+        <v>28533074.5</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="8">
-        <f>D87</f>
-        <v>28767477.5</v>
-      </c>
-      <c r="B87" s="3">
+      <c r="A87" s="3">
         <v>38384</v>
       </c>
+      <c r="B87" s="8">
+        <v>28767478</v>
+      </c>
       <c r="C87" s="29">
-        <f>D87</f>
-        <v>28767477.5</v>
-      </c>
-      <c r="D87" s="4">
+        <f t="shared" si="2"/>
+        <v>373504</v>
+      </c>
+      <c r="D87">
         <f t="shared" si="3"/>
         <v>28767477.5</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="8">
+      <c r="A88" s="3">
+        <v>38412</v>
+      </c>
+      <c r="B88" s="8">
         <v>29140981</v>
-      </c>
-      <c r="B88" s="3">
-        <v>38412</v>
       </c>
       <c r="C88" s="29">
         <f t="shared" si="2"/>
-        <v>373503.5</v>
-      </c>
-      <c r="D88" s="4">
+        <v>373503</v>
+      </c>
+      <c r="D88">
         <f t="shared" si="3"/>
-        <v>28446874.75</v>
+        <v>28446875</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="8">
+      <c r="A89" s="3">
+        <v>38443</v>
+      </c>
+      <c r="B89" s="8">
         <v>28126272</v>
-      </c>
-      <c r="B89" s="3">
-        <v>38443</v>
       </c>
       <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>-1014709</v>
       </c>
-      <c r="D89" s="4">
+      <c r="D89">
         <f t="shared" si="3"/>
         <v>29146264</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="8">
+      <c r="A90" s="3">
+        <v>38473</v>
+      </c>
+      <c r="B90" s="8">
         <v>29151547</v>
-      </c>
-      <c r="B90" s="3">
-        <v>38473</v>
       </c>
       <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>1025275</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90">
         <f t="shared" si="3"/>
         <v>28214881.5</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="8">
+      <c r="A91" s="3">
+        <v>38504</v>
+      </c>
+      <c r="B91" s="8">
         <v>28303491</v>
-      </c>
-      <c r="B91" s="3">
-        <v>38504</v>
       </c>
       <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-848056</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91">
         <f t="shared" si="3"/>
         <v>29402997</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="8">
+      <c r="A92" s="3">
+        <v>38534</v>
+      </c>
+      <c r="B92" s="8">
         <v>29654447</v>
-      </c>
-      <c r="B92" s="3">
-        <v>38534</v>
       </c>
       <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>1350956</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92">
         <f t="shared" si="3"/>
         <v>29196453</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="8">
+      <c r="A93" s="3">
+        <v>38565</v>
+      </c>
+      <c r="B93" s="8">
         <v>30089415</v>
-      </c>
-      <c r="B93" s="3">
-        <v>38565</v>
       </c>
       <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>434968</v>
       </c>
-      <c r="D93" s="4">
+      <c r="D93">
         <f t="shared" si="3"/>
-        <v>29846313.5</v>
+        <v>28343494.5</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="8">
-        <f>D94</f>
-        <v>30038180</v>
-      </c>
-      <c r="B94" s="3">
+      <c r="A94" s="3">
         <v>38596</v>
       </c>
+      <c r="B94" s="8">
+        <v>27032542</v>
+      </c>
       <c r="C94" s="29">
-        <f>D94</f>
-        <v>30038180</v>
-      </c>
-      <c r="D94" s="4">
+        <f t="shared" si="2"/>
+        <v>-3056873</v>
+      </c>
+      <c r="D94">
         <f t="shared" si="3"/>
         <v>30038180</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="8">
+      <c r="A95" s="3">
+        <v>38626</v>
+      </c>
+      <c r="B95" s="8">
         <v>29986945</v>
-      </c>
-      <c r="B95" s="3">
-        <v>38626</v>
       </c>
       <c r="C95" s="29">
         <f t="shared" si="2"/>
-        <v>-51235</v>
-      </c>
-      <c r="D95" s="4">
+        <v>2954403</v>
+      </c>
+      <c r="D95">
         <f t="shared" si="3"/>
-        <v>29704567.5</v>
+        <v>28201748.5</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="8">
+      <c r="A96" s="3">
+        <v>38657</v>
+      </c>
+      <c r="B96" s="8">
         <v>29370955</v>
-      </c>
-      <c r="B96" s="3">
-        <v>38657</v>
       </c>
       <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>-615990</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96">
         <f t="shared" si="3"/>
         <v>30175004</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="8">
+      <c r="A97" s="3">
+        <v>38687</v>
+      </c>
+      <c r="B97" s="8">
         <v>30363063</v>
-      </c>
-      <c r="B97" s="3">
-        <v>38687</v>
       </c>
       <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>992108</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97">
         <f t="shared" si="3"/>
         <v>29890670.5</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="8">
+      <c r="A98" s="3">
+        <v>38718</v>
+      </c>
+      <c r="B98" s="8">
         <v>30410386</v>
-      </c>
-      <c r="B98" s="3">
-        <v>38718</v>
       </c>
       <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>47323</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98">
         <f t="shared" si="3"/>
-        <v>30409292.75</v>
+        <v>30409293</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="8">
-        <f>D99</f>
-        <v>30455522.5</v>
-      </c>
-      <c r="B99" s="3">
+      <c r="A99" s="3">
         <v>38749</v>
       </c>
+      <c r="B99" s="8">
+        <v>30455523</v>
+      </c>
       <c r="C99" s="29">
-        <f>D99</f>
-        <v>30455522.5</v>
-      </c>
-      <c r="D99" s="4">
+        <f t="shared" si="2"/>
+        <v>45137</v>
+      </c>
+      <c r="D99">
         <f t="shared" si="3"/>
         <v>30455522.5</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="8">
+      <c r="A100" s="3">
+        <v>38777</v>
+      </c>
+      <c r="B100" s="8">
         <v>30500659</v>
-      </c>
-      <c r="B100" s="3">
-        <v>38777</v>
       </c>
       <c r="C100" s="29">
         <f t="shared" si="2"/>
-        <v>45136.5</v>
-      </c>
-      <c r="D100" s="4">
+        <v>45136</v>
+      </c>
+      <c r="D100">
         <f t="shared" si="3"/>
-        <v>29887124.75</v>
+        <v>29887125</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="8">
+      <c r="A101" s="3">
+        <v>38808</v>
+      </c>
+      <c r="B101" s="8">
         <v>29318727</v>
-      </c>
-      <c r="B101" s="3">
-        <v>38808</v>
       </c>
       <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>-1181932</v>
       </c>
-      <c r="D101" s="4">
+      <c r="D101">
         <f t="shared" si="3"/>
         <v>30630264.5</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="8">
+      <c r="A102" s="3">
+        <v>38838</v>
+      </c>
+      <c r="B102" s="8">
         <v>30759870</v>
-      </c>
-      <c r="B102" s="3">
-        <v>38838</v>
       </c>
       <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>1441143</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102">
         <f t="shared" si="3"/>
         <v>29421272</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="8">
+      <c r="A103" s="3">
+        <v>38869</v>
+      </c>
+      <c r="B103" s="8">
         <v>29523817</v>
-      </c>
-      <c r="B103" s="3">
-        <v>38869</v>
       </c>
       <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-1236053</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103">
         <f t="shared" si="3"/>
         <v>30614159.5</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="8">
+      <c r="A104" s="3">
+        <v>38899</v>
+      </c>
+      <c r="B104" s="8">
         <v>30468449</v>
-      </c>
-      <c r="B104" s="3">
-        <v>38899</v>
       </c>
       <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>944632</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104">
         <f t="shared" si="3"/>
         <v>29971316</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="8">
+      <c r="A105" s="3">
+        <v>38930</v>
+      </c>
+      <c r="B105" s="8">
         <v>30418815</v>
-      </c>
-      <c r="B105" s="3">
-        <v>38930</v>
       </c>
       <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>-49634</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105">
         <f t="shared" si="3"/>
         <v>30027853</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="8">
+      <c r="A106" s="3">
+        <v>38961</v>
+      </c>
+      <c r="B106" s="8">
         <v>29587257</v>
-      </c>
-      <c r="B106" s="3">
-        <v>38961</v>
       </c>
       <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>-831558</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106">
         <f t="shared" si="3"/>
         <v>30513394.5</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="8">
+      <c r="A107" s="3">
+        <v>38991</v>
+      </c>
+      <c r="B107" s="8">
         <v>30607974</v>
-      </c>
-      <c r="B107" s="3">
-        <v>38991</v>
       </c>
       <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>1020717</v>
       </c>
-      <c r="D107" s="4">
+      <c r="D107">
         <f t="shared" si="3"/>
         <v>29537460</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="8">
+      <c r="A108" s="3">
+        <v>39022</v>
+      </c>
+      <c r="B108" s="8">
         <v>29487663</v>
-      </c>
-      <c r="B108" s="3">
-        <v>39022</v>
       </c>
       <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>-1120311</v>
       </c>
-      <c r="D108" s="4">
+      <c r="D108">
         <f t="shared" si="3"/>
         <v>30474674.5</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="8">
+      <c r="A109" s="3">
+        <v>39052</v>
+      </c>
+      <c r="B109" s="8">
         <v>30341375</v>
-      </c>
-      <c r="B109" s="3">
-        <v>39052</v>
       </c>
       <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>853712</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D109">
         <f t="shared" si="3"/>
         <v>29633944.5</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="8">
+      <c r="A110" s="3">
+        <v>39083</v>
+      </c>
+      <c r="B110" s="8">
         <v>29780226</v>
-      </c>
-      <c r="B110" s="3">
-        <v>39083</v>
       </c>
       <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>-561149</v>
       </c>
-      <c r="D110" s="4">
+      <c r="D110">
         <f t="shared" si="3"/>
-        <v>30281725.25</v>
+        <v>30281725.5</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="8">
-        <f>D111</f>
-        <v>30222075.5</v>
-      </c>
-      <c r="B111" s="3">
+      <c r="A111" s="3">
         <v>39114</v>
       </c>
+      <c r="B111" s="8">
+        <v>30222076</v>
+      </c>
       <c r="C111" s="29">
-        <f>D111</f>
-        <v>30222075.5</v>
-      </c>
-      <c r="D111" s="4">
+        <f t="shared" si="2"/>
+        <v>441850</v>
+      </c>
+      <c r="D111">
         <f t="shared" si="3"/>
         <v>30222075.5</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="8">
+      <c r="A112" s="3">
+        <v>39142</v>
+      </c>
+      <c r="B112" s="8">
         <v>30663925</v>
-      </c>
-      <c r="B112" s="3">
-        <v>39142</v>
       </c>
       <c r="C112" s="29">
         <f t="shared" si="2"/>
-        <v>441849.5</v>
-      </c>
-      <c r="D112" s="4">
+        <v>441849</v>
+      </c>
+      <c r="D112">
         <f t="shared" si="3"/>
-        <v>29960444.75</v>
+        <v>29960445</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="8">
+      <c r="A113" s="3">
+        <v>39173</v>
+      </c>
+      <c r="B113" s="8">
         <v>29698814</v>
-      </c>
-      <c r="B113" s="3">
-        <v>39173</v>
       </c>
       <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>-965111</v>
       </c>
-      <c r="D113" s="4">
+      <c r="D113">
         <f t="shared" si="3"/>
         <v>30815143</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="8">
+      <c r="A114" s="3">
+        <v>39203</v>
+      </c>
+      <c r="B114" s="8">
         <v>30966361</v>
-      </c>
-      <c r="B114" s="3">
-        <v>39203</v>
       </c>
       <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>1267547</v>
       </c>
-      <c r="D114" s="4">
+      <c r="D114">
         <f t="shared" si="3"/>
         <v>29473581</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="8">
+      <c r="A115" s="3">
+        <v>39234</v>
+      </c>
+      <c r="B115" s="8">
         <v>29248348</v>
-      </c>
-      <c r="B115" s="3">
-        <v>39234</v>
       </c>
       <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>-1718013</v>
       </c>
-      <c r="D115" s="4">
+      <c r="D115">
         <f t="shared" si="3"/>
         <v>30530592</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="8">
+      <c r="A116" s="3">
+        <v>39264</v>
+      </c>
+      <c r="B116" s="8">
         <v>30094823</v>
-      </c>
-      <c r="B116" s="3">
-        <v>39264</v>
       </c>
       <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>846475</v>
       </c>
-      <c r="D116" s="4">
+      <c r="D116">
         <f t="shared" si="3"/>
         <v>29840463.5</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="8">
+      <c r="A117" s="3">
+        <v>39295</v>
+      </c>
+      <c r="B117" s="8">
         <v>30432579</v>
-      </c>
-      <c r="B117" s="3">
-        <v>39295</v>
       </c>
       <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>337756</v>
       </c>
-      <c r="D117" s="4">
+      <c r="D117">
         <f t="shared" si="3"/>
         <v>29667515</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="8">
+      <c r="A118" s="3">
+        <v>39326</v>
+      </c>
+      <c r="B118" s="8">
         <v>29240207</v>
-      </c>
-      <c r="B118" s="3">
-        <v>39326</v>
       </c>
       <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>-1192372</v>
       </c>
-      <c r="D118" s="4">
+      <c r="D118">
         <f t="shared" si="3"/>
         <v>30207540.5</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="8">
+      <c r="A119" s="3">
+        <v>39356</v>
+      </c>
+      <c r="B119" s="8">
         <v>29982502</v>
-      </c>
-      <c r="B119" s="3">
-        <v>39356</v>
       </c>
       <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>742295</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119">
         <f t="shared" si="3"/>
         <v>29385295.5</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="8">
+      <c r="A120" s="3">
+        <v>39387</v>
+      </c>
+      <c r="B120" s="8">
         <v>29530384</v>
-      </c>
-      <c r="B120" s="3">
-        <v>39387</v>
       </c>
       <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>-452118</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D120">
         <f t="shared" si="3"/>
         <v>30214475</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="8">
+      <c r="A121" s="3">
+        <v>39417</v>
+      </c>
+      <c r="B121" s="8">
         <v>30446448</v>
-      </c>
-      <c r="B121" s="3">
-        <v>39417</v>
       </c>
       <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>916064</v>
       </c>
-      <c r="D121" s="4">
+      <c r="D121">
         <f t="shared" si="3"/>
         <v>29961560.5</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="8">
+      <c r="A122" s="3">
+        <v>39448</v>
+      </c>
+      <c r="B122" s="8">
         <v>30392737</v>
-      </c>
-      <c r="B122" s="3">
-        <v>39448</v>
       </c>
       <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>-53711</v>
       </c>
-      <c r="D122" s="4">
+      <c r="D122">
         <f t="shared" si="3"/>
         <v>29635341.5</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="8">
+      <c r="A123" s="3">
+        <v>39479</v>
+      </c>
+      <c r="B123" s="8">
         <v>28824235</v>
-      </c>
-      <c r="B123" s="3">
-        <v>39479</v>
       </c>
       <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>-1568502</v>
       </c>
-      <c r="D123" s="4">
+      <c r="D123">
         <f t="shared" si="3"/>
         <v>30468740.5</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="8">
+      <c r="A124" s="3">
+        <v>39508</v>
+      </c>
+      <c r="B124" s="8">
         <v>30544744</v>
-      </c>
-      <c r="B124" s="3">
-        <v>39508</v>
       </c>
       <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>1720509</v>
       </c>
-      <c r="D124" s="4">
+      <c r="D124">
         <f t="shared" si="3"/>
         <v>29198730</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="8">
+      <c r="A125" s="3">
+        <v>39539</v>
+      </c>
+      <c r="B125" s="8">
         <v>29573225</v>
-      </c>
-      <c r="B125" s="3">
-        <v>39539</v>
       </c>
       <c r="C125" s="29">
         <f t="shared" si="2"/>
         <v>-971519</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D125">
         <f t="shared" si="3"/>
         <v>31028998</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="8">
+      <c r="A126" s="3">
+        <v>39569</v>
+      </c>
+      <c r="B126" s="8">
         <v>31513252</v>
-      </c>
-      <c r="B126" s="3">
-        <v>39569</v>
       </c>
       <c r="C126" s="29">
         <f t="shared" si="2"/>
         <v>1940027</v>
       </c>
-      <c r="D126" s="4">
+      <c r="D126">
         <f t="shared" si="3"/>
         <v>30011416.5</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="8">
+      <c r="A127" s="3">
+        <v>39600</v>
+      </c>
+      <c r="B127" s="8">
         <v>30449608</v>
-      </c>
-      <c r="B127" s="3">
-        <v>39600</v>
       </c>
       <c r="C127" s="29">
         <f t="shared" si="2"/>
         <v>-1063644</v>
       </c>
-      <c r="D127" s="4">
+      <c r="D127">
         <f t="shared" si="3"/>
         <v>31661416.5</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="8">
+      <c r="A128" s="3">
+        <v>39630</v>
+      </c>
+      <c r="B128" s="8">
         <v>31809581</v>
-      </c>
-      <c r="B128" s="3">
-        <v>39630</v>
       </c>
       <c r="C128" s="29">
         <f t="shared" si="2"/>
         <v>1359973</v>
       </c>
-      <c r="D128" s="4">
+      <c r="D128">
         <f t="shared" si="3"/>
         <v>31174362</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="8">
+      <c r="A129" s="3">
+        <v>39661</v>
+      </c>
+      <c r="B129" s="8">
         <v>31899116</v>
-      </c>
-      <c r="B129" s="3">
-        <v>39661</v>
       </c>
       <c r="C129" s="29">
         <f t="shared" si="2"/>
         <v>89535</v>
       </c>
-      <c r="D129" s="4">
+      <c r="D129">
         <f t="shared" si="3"/>
-        <v>31773657.25</v>
+        <v>31773657.5</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="8">
-        <f>D130</f>
-        <v>31737733.5</v>
-      </c>
-      <c r="B130" s="3">
+      <c r="A130" s="3">
         <v>39692</v>
       </c>
+      <c r="B130" s="8">
+        <v>31737734</v>
+      </c>
       <c r="C130" s="29">
-        <f>D130</f>
-        <v>31737733.5</v>
-      </c>
-      <c r="D130" s="4">
+        <f t="shared" si="2"/>
+        <v>-161382</v>
+      </c>
+      <c r="D130">
         <f t="shared" si="3"/>
         <v>31737733.5</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="8">
+      <c r="A131" s="3">
+        <v>39722</v>
+      </c>
+      <c r="B131" s="8">
         <v>31576351</v>
-      </c>
-      <c r="B131" s="3">
-        <v>39722</v>
       </c>
       <c r="C131" s="29">
         <f t="shared" si="2"/>
-        <v>-161382.5</v>
-      </c>
-      <c r="D131" s="4">
+        <v>-161383</v>
+      </c>
+      <c r="D131">
         <f t="shared" si="3"/>
-        <v>31291376.25</v>
+        <v>31291376.5</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="8">
+      <c r="A132" s="3">
+        <v>39753</v>
+      </c>
+      <c r="B132" s="8">
         <v>30845019</v>
       </c>
-      <c r="B132" s="3">
-        <v>39753</v>
-      </c>
       <c r="C132" s="29">
-        <f t="shared" ref="C132:C194" si="4">A132-A131</f>
+        <f t="shared" ref="C132:C195" si="4">B132-B131</f>
         <v>-731332</v>
       </c>
-      <c r="D132" s="4">
-        <f t="shared" ref="D132:D195" si="5">(A131+A133)/2</f>
+      <c r="D132">
+        <f t="shared" ref="D132:D195" si="5">(B131+B133)/2</f>
         <v>31353373</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="8">
+      <c r="A133" s="3">
+        <v>39783</v>
+      </c>
+      <c r="B133" s="8">
         <v>31130395</v>
-      </c>
-      <c r="B133" s="3">
-        <v>39783</v>
       </c>
       <c r="C133" s="29">
         <f t="shared" si="4"/>
         <v>285376</v>
       </c>
-      <c r="D133" s="4">
+      <c r="D133">
         <f t="shared" si="5"/>
         <v>30759969.5</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="8">
+      <c r="A134" s="3">
+        <v>39814</v>
+      </c>
+      <c r="B134" s="8">
         <v>30674920</v>
-      </c>
-      <c r="B134" s="3">
-        <v>39814</v>
       </c>
       <c r="C134" s="29">
         <f t="shared" si="4"/>
         <v>-455475</v>
       </c>
-      <c r="D134" s="4">
+      <c r="D134">
         <f t="shared" si="5"/>
-        <v>30803251.75</v>
+        <v>30803252</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="8">
-        <f>D135</f>
-        <v>30476108.5</v>
-      </c>
-      <c r="B135" s="3">
+      <c r="A135" s="3">
         <v>39845</v>
       </c>
+      <c r="B135" s="8">
+        <v>30476109</v>
+      </c>
       <c r="C135" s="29">
-        <f>D135</f>
-        <v>30476108.5</v>
-      </c>
-      <c r="D135" s="4">
+        <f t="shared" si="4"/>
+        <v>-198811</v>
+      </c>
+      <c r="D135">
         <f t="shared" si="5"/>
         <v>30476108.5</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="8">
+      <c r="A136" s="3">
+        <v>39873</v>
+      </c>
+      <c r="B136" s="8">
         <v>30277297</v>
-      </c>
-      <c r="B136" s="3">
-        <v>39873</v>
       </c>
       <c r="C136" s="29">
         <f t="shared" si="4"/>
-        <v>-198811.5</v>
-      </c>
-      <c r="D136" s="4">
+        <v>-198812</v>
+      </c>
+      <c r="D136">
         <f t="shared" si="5"/>
-        <v>29874037.75</v>
+        <v>29874038</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="8">
+      <c r="A137" s="3">
+        <v>39904</v>
+      </c>
+      <c r="B137" s="8">
         <v>29271967</v>
-      </c>
-      <c r="B137" s="3">
-        <v>39904</v>
       </c>
       <c r="C137" s="29">
         <f t="shared" si="4"/>
         <v>-1005330</v>
       </c>
-      <c r="D137" s="4">
+      <c r="D137">
         <f t="shared" si="5"/>
         <v>30113698.5</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="8">
+      <c r="A138" s="3">
+        <v>39934</v>
+      </c>
+      <c r="B138" s="8">
         <v>29950100</v>
-      </c>
-      <c r="B138" s="3">
-        <v>39934</v>
       </c>
       <c r="C138" s="29">
         <f t="shared" si="4"/>
         <v>678133</v>
       </c>
-      <c r="D138" s="4">
+      <c r="D138">
         <f t="shared" si="5"/>
         <v>29151989</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="8">
+      <c r="A139" s="3">
+        <v>39965</v>
+      </c>
+      <c r="B139" s="8">
         <v>29032011</v>
-      </c>
-      <c r="B139" s="3">
-        <v>39965</v>
       </c>
       <c r="C139" s="29">
         <f t="shared" si="4"/>
         <v>-918089</v>
       </c>
-      <c r="D139" s="4">
+      <c r="D139">
         <f t="shared" si="5"/>
         <v>30090932</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="8">
+      <c r="A140" s="3">
+        <v>39995</v>
+      </c>
+      <c r="B140" s="8">
         <v>30231764</v>
-      </c>
-      <c r="B140" s="3">
-        <v>39995</v>
       </c>
       <c r="C140" s="29">
         <f t="shared" si="4"/>
         <v>1199753</v>
       </c>
-      <c r="D140" s="4">
+      <c r="D140">
         <f t="shared" si="5"/>
         <v>29593375</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="8">
+      <c r="A141" s="3">
+        <v>40026</v>
+      </c>
+      <c r="B141" s="8">
         <v>30154739</v>
-      </c>
-      <c r="B141" s="3">
-        <v>40026</v>
       </c>
       <c r="C141" s="29">
         <f t="shared" si="4"/>
         <v>-77025</v>
       </c>
-      <c r="D141" s="4">
+      <c r="D141">
         <f t="shared" si="5"/>
         <v>29653222.5</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="8">
+      <c r="A142" s="3">
+        <v>40057</v>
+      </c>
+      <c r="B142" s="8">
         <v>29074681</v>
-      </c>
-      <c r="B142" s="3">
-        <v>40057</v>
       </c>
       <c r="C142" s="29">
         <f t="shared" si="4"/>
         <v>-1080058</v>
       </c>
-      <c r="D142" s="4">
+      <c r="D142">
         <f t="shared" si="5"/>
         <v>29758753</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="8">
+      <c r="A143" s="3">
+        <v>40087</v>
+      </c>
+      <c r="B143" s="8">
         <v>29362767</v>
-      </c>
-      <c r="B143" s="3">
-        <v>40087</v>
       </c>
       <c r="C143" s="29">
         <f t="shared" si="4"/>
         <v>288086</v>
       </c>
-      <c r="D143" s="4">
+      <c r="D143">
         <f t="shared" si="5"/>
         <v>28777251</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="8">
+      <c r="A144" s="3">
+        <v>40118</v>
+      </c>
+      <c r="B144" s="8">
         <v>28479821</v>
-      </c>
-      <c r="B144" s="3">
-        <v>40118</v>
       </c>
       <c r="C144" s="29">
         <f t="shared" si="4"/>
         <v>-882946</v>
       </c>
-      <c r="D144" s="4">
+      <c r="D144">
         <f t="shared" si="5"/>
         <v>29535987</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="8">
+      <c r="A145" s="3">
+        <v>40148</v>
+      </c>
+      <c r="B145" s="8">
         <v>29709207</v>
-      </c>
-      <c r="B145" s="3">
-        <v>40148</v>
       </c>
       <c r="C145" s="29">
         <f t="shared" si="4"/>
         <v>1229386</v>
       </c>
-      <c r="D145" s="4">
+      <c r="D145">
         <f t="shared" si="5"/>
         <v>29052321</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="8">
+      <c r="A146" s="3">
+        <v>40179</v>
+      </c>
+      <c r="B146" s="8">
         <v>29624821</v>
-      </c>
-      <c r="B146" s="3">
-        <v>40179</v>
       </c>
       <c r="C146" s="29">
         <f t="shared" si="4"/>
         <v>-84386</v>
       </c>
-      <c r="D146" s="4">
+      <c r="D146">
         <f t="shared" si="5"/>
         <v>29779152</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="8">
-        <f>D147</f>
+      <c r="A147" s="3">
+        <v>40210</v>
+      </c>
+      <c r="B147" s="8">
         <v>29849097</v>
       </c>
-      <c r="B147" s="3">
-        <v>40210</v>
-      </c>
       <c r="C147" s="29">
-        <f>D147</f>
-        <v>29849097</v>
-      </c>
-      <c r="D147" s="4">
+        <f t="shared" si="4"/>
+        <v>224276</v>
+      </c>
+      <c r="D147">
         <f t="shared" si="5"/>
         <v>29849097</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="8">
+      <c r="A148" s="3">
+        <v>40238</v>
+      </c>
+      <c r="B148" s="8">
         <v>30073373</v>
-      </c>
-      <c r="B148" s="3">
-        <v>40238</v>
       </c>
       <c r="C148" s="29">
         <f t="shared" si="4"/>
         <v>224276</v>
       </c>
-      <c r="D148" s="4">
+      <c r="D148">
         <f t="shared" si="5"/>
         <v>29664669.5</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="8">
+      <c r="A149" s="3">
+        <v>40269</v>
+      </c>
+      <c r="B149" s="8">
         <v>29480242</v>
-      </c>
-      <c r="B149" s="3">
-        <v>40269</v>
       </c>
       <c r="C149" s="29">
         <f t="shared" si="4"/>
         <v>-593131</v>
       </c>
-      <c r="D149" s="4">
+      <c r="D149">
         <f t="shared" si="5"/>
         <v>30431430</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="8">
+      <c r="A150" s="3">
+        <v>40299</v>
+      </c>
+      <c r="B150" s="8">
         <v>30789487</v>
-      </c>
-      <c r="B150" s="3">
-        <v>40299</v>
       </c>
       <c r="C150" s="29">
         <f t="shared" si="4"/>
         <v>1309245</v>
       </c>
-      <c r="D150" s="4">
+      <c r="D150">
         <f t="shared" si="5"/>
         <v>29636917</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="8">
+      <c r="A151" s="3">
+        <v>40330</v>
+      </c>
+      <c r="B151" s="8">
         <v>29793592</v>
-      </c>
-      <c r="B151" s="3">
-        <v>40330</v>
       </c>
       <c r="C151" s="29">
         <f t="shared" si="4"/>
         <v>-995895</v>
       </c>
-      <c r="D151" s="4">
+      <c r="D151">
         <f t="shared" si="5"/>
         <v>30702930.5</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="8">
+      <c r="A152" s="3">
+        <v>40360</v>
+      </c>
+      <c r="B152" s="8">
         <v>30616374</v>
-      </c>
-      <c r="B152" s="3">
-        <v>40360</v>
       </c>
       <c r="C152" s="29">
         <f t="shared" si="4"/>
         <v>822782</v>
       </c>
-      <c r="D152" s="4">
+      <c r="D152">
         <f t="shared" si="5"/>
         <v>30286697.5</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="8">
+      <c r="A153" s="3">
+        <v>40391</v>
+      </c>
+      <c r="B153" s="8">
         <v>30779803</v>
-      </c>
-      <c r="B153" s="3">
-        <v>40391</v>
       </c>
       <c r="C153" s="29">
         <f t="shared" si="4"/>
         <v>163429</v>
       </c>
-      <c r="D153" s="4">
+      <c r="D153">
         <f t="shared" si="5"/>
         <v>30356526.5</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="8">
+      <c r="A154" s="3">
+        <v>40422</v>
+      </c>
+      <c r="B154" s="8">
         <v>30096679</v>
-      </c>
-      <c r="B154" s="3">
-        <v>40422</v>
       </c>
       <c r="C154" s="29">
         <f t="shared" si="4"/>
         <v>-683124</v>
       </c>
-      <c r="D154" s="4">
+      <c r="D154">
         <f t="shared" si="5"/>
         <v>30860350.5</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="8">
+      <c r="A155" s="3">
+        <v>40452</v>
+      </c>
+      <c r="B155" s="8">
         <v>30940898</v>
-      </c>
-      <c r="B155" s="3">
-        <v>40452</v>
       </c>
       <c r="C155" s="29">
         <f t="shared" si="4"/>
         <v>844219</v>
       </c>
-      <c r="D155" s="4">
+      <c r="D155">
         <f t="shared" si="5"/>
         <v>30114293</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="8">
+      <c r="A156" s="3">
+        <v>40483</v>
+      </c>
+      <c r="B156" s="8">
         <v>30131907</v>
-      </c>
-      <c r="B156" s="3">
-        <v>40483</v>
       </c>
       <c r="C156" s="29">
         <f t="shared" si="4"/>
         <v>-808991</v>
       </c>
-      <c r="D156" s="4">
+      <c r="D156">
         <f t="shared" si="5"/>
         <v>30825560.5</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="8">
+      <c r="A157" s="3">
+        <v>40513</v>
+      </c>
+      <c r="B157" s="8">
         <v>30710223</v>
-      </c>
-      <c r="B157" s="3">
-        <v>40513</v>
       </c>
       <c r="C157" s="29">
         <f t="shared" si="4"/>
         <v>578316</v>
       </c>
-      <c r="D157" s="4">
+      <c r="D157">
         <f t="shared" si="5"/>
         <v>30383188</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="8">
+      <c r="A158" s="3">
+        <v>40544</v>
+      </c>
+      <c r="B158" s="8">
         <v>30634469</v>
-      </c>
-      <c r="B158" s="3">
-        <v>40544</v>
       </c>
       <c r="C158" s="29">
         <f t="shared" si="4"/>
         <v>-75754</v>
       </c>
-      <c r="D158" s="4">
+      <c r="D158">
         <f t="shared" si="5"/>
-        <v>30769004.25</v>
+        <v>30769004.5</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="8">
-        <f>D159</f>
-        <v>30827785.5</v>
-      </c>
-      <c r="B159" s="3">
+      <c r="A159" s="3">
         <v>40575</v>
       </c>
+      <c r="B159" s="8">
+        <v>30827786</v>
+      </c>
       <c r="C159" s="29">
-        <f>D159</f>
-        <v>30827785.5</v>
-      </c>
-      <c r="D159" s="4">
+        <f t="shared" si="4"/>
+        <v>193317</v>
+      </c>
+      <c r="D159">
         <f t="shared" si="5"/>
         <v>30827785.5</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="8">
+      <c r="A160" s="3">
+        <v>40603</v>
+      </c>
+      <c r="B160" s="8">
         <v>31021102</v>
-      </c>
-      <c r="B160" s="3">
-        <v>40603</v>
       </c>
       <c r="C160" s="29">
         <f t="shared" si="4"/>
-        <v>193316.5</v>
-      </c>
-      <c r="D160" s="4">
+        <v>193316</v>
+      </c>
+      <c r="D160">
         <f t="shared" si="5"/>
-        <v>30243762.75</v>
+        <v>30243763</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="8">
+      <c r="A161" s="3">
+        <v>40634</v>
+      </c>
+      <c r="B161" s="8">
         <v>29659740</v>
-      </c>
-      <c r="B161" s="3">
-        <v>40634</v>
       </c>
       <c r="C161" s="29">
         <f t="shared" si="4"/>
         <v>-1361362</v>
       </c>
-      <c r="D161" s="4">
+      <c r="D161">
         <f t="shared" si="5"/>
         <v>31175637</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="8">
+      <c r="A162" s="3">
+        <v>40664</v>
+      </c>
+      <c r="B162" s="8">
         <v>31330172</v>
-      </c>
-      <c r="B162" s="3">
-        <v>40664</v>
       </c>
       <c r="C162" s="29">
         <f t="shared" si="4"/>
         <v>1670432</v>
       </c>
-      <c r="D162" s="4">
+      <c r="D162">
         <f t="shared" si="5"/>
         <v>30002790</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="8">
+      <c r="A163" s="3">
+        <v>40695</v>
+      </c>
+      <c r="B163" s="8">
         <v>30345840</v>
-      </c>
-      <c r="B163" s="3">
-        <v>40695</v>
       </c>
       <c r="C163" s="29">
         <f t="shared" si="4"/>
         <v>-984332</v>
       </c>
-      <c r="D163" s="4">
+      <c r="D163">
         <f t="shared" si="5"/>
         <v>31508881.5</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="8">
+      <c r="A164" s="3">
+        <v>40725</v>
+      </c>
+      <c r="B164" s="8">
         <v>31687591</v>
-      </c>
-      <c r="B164" s="3">
-        <v>40725</v>
       </c>
       <c r="C164" s="29">
         <f t="shared" si="4"/>
         <v>1341751</v>
       </c>
-      <c r="D164" s="4">
+      <c r="D164">
         <f t="shared" si="5"/>
         <v>30818450</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="8">
+      <c r="A165" s="3">
+        <v>40756</v>
+      </c>
+      <c r="B165" s="8">
         <v>31291060</v>
-      </c>
-      <c r="B165" s="3">
-        <v>40756</v>
       </c>
       <c r="C165" s="29">
         <f t="shared" si="4"/>
         <v>-396531</v>
       </c>
-      <c r="D165" s="4">
+      <c r="D165">
         <f t="shared" si="5"/>
         <v>30561827.5</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="8">
+      <c r="A166" s="3">
+        <v>40787</v>
+      </c>
+      <c r="B166" s="8">
         <v>29436064</v>
-      </c>
-      <c r="B166" s="3">
-        <v>40787</v>
       </c>
       <c r="C166" s="29">
         <f t="shared" si="4"/>
         <v>-1854996</v>
       </c>
-      <c r="D166" s="4">
+      <c r="D166">
         <f t="shared" si="5"/>
         <v>31569684</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="8">
+      <c r="A167" s="3">
+        <v>40817</v>
+      </c>
+      <c r="B167" s="8">
         <v>31848308</v>
-      </c>
-      <c r="B167" s="3">
-        <v>40817</v>
       </c>
       <c r="C167" s="29">
         <f t="shared" si="4"/>
         <v>2412244</v>
       </c>
-      <c r="D167" s="4">
+      <c r="D167">
         <f t="shared" si="5"/>
         <v>30369225.5</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="8">
+      <c r="A168" s="3">
+        <v>40848</v>
+      </c>
+      <c r="B168" s="8">
         <v>31302387</v>
-      </c>
-      <c r="B168" s="3">
-        <v>40848</v>
       </c>
       <c r="C168" s="29">
         <f t="shared" si="4"/>
         <v>-545921</v>
       </c>
-      <c r="D168" s="4">
+      <c r="D168">
         <f t="shared" si="5"/>
         <v>31893827</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="8">
+      <c r="A169" s="3">
+        <v>40878</v>
+      </c>
+      <c r="B169" s="8">
         <v>31939346</v>
-      </c>
-      <c r="B169" s="3">
-        <v>40878</v>
       </c>
       <c r="C169" s="29">
         <f t="shared" si="4"/>
         <v>636959</v>
       </c>
-      <c r="D169" s="4">
+      <c r="D169">
         <f t="shared" si="5"/>
         <v>31633199</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="8">
+      <c r="A170" s="3">
+        <v>40909</v>
+      </c>
+      <c r="B170" s="8">
         <v>31964011</v>
-      </c>
-      <c r="B170" s="3">
-        <v>40909</v>
       </c>
       <c r="C170" s="29">
         <f t="shared" si="4"/>
         <v>24665</v>
       </c>
-      <c r="D170" s="4">
+      <c r="D170">
         <f t="shared" si="5"/>
         <v>31117195</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="8">
+      <c r="A171" s="3">
+        <v>40940</v>
+      </c>
+      <c r="B171" s="8">
         <v>30295044</v>
-      </c>
-      <c r="B171" s="3">
-        <v>40940</v>
       </c>
       <c r="C171" s="29">
         <f t="shared" si="4"/>
         <v>-1668967</v>
       </c>
-      <c r="D171" s="4">
+      <c r="D171">
         <f t="shared" si="5"/>
         <v>32091659</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="8">
+      <c r="A172" s="3">
+        <v>40969</v>
+      </c>
+      <c r="B172" s="8">
         <v>32219307</v>
-      </c>
-      <c r="B172" s="3">
-        <v>40969</v>
       </c>
       <c r="C172" s="29">
         <f t="shared" si="4"/>
         <v>1924263</v>
       </c>
-      <c r="D172" s="4">
+      <c r="D172">
         <f t="shared" si="5"/>
         <v>30978495.5</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="8">
+      <c r="A173" s="3">
+        <v>41000</v>
+      </c>
+      <c r="B173" s="8">
         <v>31661947</v>
-      </c>
-      <c r="B173" s="3">
-        <v>41000</v>
       </c>
       <c r="C173" s="29">
         <f t="shared" si="4"/>
         <v>-557360</v>
       </c>
-      <c r="D173" s="4">
+      <c r="D173">
         <f t="shared" si="5"/>
         <v>32196207</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="8">
+      <c r="A174" s="3">
+        <v>41030</v>
+      </c>
+      <c r="B174" s="8">
         <v>32173107</v>
-      </c>
-      <c r="B174" s="3">
-        <v>41030</v>
       </c>
       <c r="C174" s="29">
         <f t="shared" si="4"/>
         <v>511160</v>
       </c>
-      <c r="D174" s="4">
+      <c r="D174">
         <f t="shared" si="5"/>
         <v>31881857.5</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="8">
+      <c r="A175" s="3">
+        <v>41061</v>
+      </c>
+      <c r="B175" s="8">
         <v>32101768</v>
-      </c>
-      <c r="B175" s="3">
-        <v>41061</v>
       </c>
       <c r="C175" s="29">
         <f t="shared" si="4"/>
         <v>-71339</v>
       </c>
-      <c r="D175" s="4">
+      <c r="D175">
         <f t="shared" si="5"/>
         <v>32616368</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="8">
+      <c r="A176" s="3">
+        <v>41091</v>
+      </c>
+      <c r="B176" s="8">
         <v>33059629</v>
-      </c>
-      <c r="B176" s="3">
-        <v>41091</v>
       </c>
       <c r="C176" s="29">
         <f t="shared" si="4"/>
         <v>957861</v>
       </c>
-      <c r="D176" s="4">
+      <c r="D176">
         <f t="shared" si="5"/>
         <v>31987017</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="8">
+      <c r="A177" s="3">
+        <v>41122</v>
+      </c>
+      <c r="B177" s="8">
         <v>31872266</v>
-      </c>
-      <c r="B177" s="3">
-        <v>41122</v>
       </c>
       <c r="C177" s="29">
         <f t="shared" si="4"/>
         <v>-1187363</v>
       </c>
-      <c r="D177" s="4">
+      <c r="D177">
         <f t="shared" si="5"/>
         <v>32471440</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="8">
+      <c r="A178" s="3">
+        <v>41153</v>
+      </c>
+      <c r="B178" s="8">
         <v>31883251</v>
-      </c>
-      <c r="B178" s="3">
-        <v>41153</v>
       </c>
       <c r="C178" s="29">
         <f t="shared" si="4"/>
         <v>10985</v>
       </c>
-      <c r="D178" s="4">
+      <c r="D178">
         <f t="shared" si="5"/>
         <v>32449189.5</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="8">
+      <c r="A179" s="3">
+        <v>41183</v>
+      </c>
+      <c r="B179" s="8">
         <v>33026113</v>
-      </c>
-      <c r="B179" s="3">
-        <v>41183</v>
       </c>
       <c r="C179" s="29">
         <f t="shared" si="4"/>
         <v>1142862</v>
       </c>
-      <c r="D179" s="4">
+      <c r="D179">
         <f t="shared" si="5"/>
         <v>32023879.5</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="8">
+      <c r="A180" s="3">
+        <v>41214</v>
+      </c>
+      <c r="B180" s="8">
         <v>32164508</v>
-      </c>
-      <c r="B180" s="3">
-        <v>41214</v>
       </c>
       <c r="C180" s="29">
         <f t="shared" si="4"/>
         <v>-861605</v>
       </c>
-      <c r="D180" s="4">
+      <c r="D180">
         <f t="shared" si="5"/>
         <v>32752224.5</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="8">
+      <c r="A181" s="3">
+        <v>41244</v>
+      </c>
+      <c r="B181" s="8">
         <v>32478336</v>
-      </c>
-      <c r="B181" s="3">
-        <v>41244</v>
       </c>
       <c r="C181" s="29">
         <f t="shared" si="4"/>
         <v>313828</v>
       </c>
-      <c r="D181" s="4">
+      <c r="D181">
         <f t="shared" si="5"/>
         <v>32249121</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="8">
+      <c r="A182" s="3">
+        <v>41275</v>
+      </c>
+      <c r="B182" s="8">
         <v>32333734</v>
-      </c>
-      <c r="B182" s="3">
-        <v>41275</v>
       </c>
       <c r="C182" s="29">
         <f t="shared" si="4"/>
         <v>-144602</v>
       </c>
-      <c r="D182" s="4">
+      <c r="D182">
         <f t="shared" si="5"/>
-        <v>32523805.75</v>
+        <v>32523806</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="8">
-        <f>D183</f>
-        <v>32569275.5</v>
-      </c>
-      <c r="B183" s="3">
+      <c r="A183" s="3">
         <v>41306</v>
       </c>
+      <c r="B183" s="8">
+        <v>32569276</v>
+      </c>
       <c r="C183" s="29">
-        <f>D183</f>
-        <v>32569275.5</v>
-      </c>
-      <c r="D183" s="4">
+        <f t="shared" si="4"/>
+        <v>235542</v>
+      </c>
+      <c r="D183">
         <f t="shared" si="5"/>
         <v>32569275.5</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="8">
+      <c r="A184" s="3">
+        <v>41334</v>
+      </c>
+      <c r="B184" s="8">
         <v>32804817</v>
-      </c>
-      <c r="B184" s="3">
-        <v>41334</v>
       </c>
       <c r="C184" s="29">
         <f t="shared" si="4"/>
-        <v>235541.5</v>
-      </c>
-      <c r="D184" s="4">
+        <v>235541</v>
+      </c>
+      <c r="D184">
         <f t="shared" si="5"/>
-        <v>31843906.25</v>
+        <v>31843906.5</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="8">
+      <c r="A185" s="3">
+        <v>41365</v>
+      </c>
+      <c r="B185" s="8">
         <v>31118537</v>
-      </c>
-      <c r="B185" s="3">
-        <v>41365</v>
       </c>
       <c r="C185" s="29">
         <f t="shared" si="4"/>
         <v>-1686280</v>
       </c>
-      <c r="D185" s="4">
+      <c r="D185">
         <f t="shared" si="5"/>
         <v>32667376.5</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="8">
+      <c r="A186" s="3">
+        <v>41395</v>
+      </c>
+      <c r="B186" s="8">
         <v>32529936</v>
-      </c>
-      <c r="B186" s="3">
-        <v>41395</v>
       </c>
       <c r="C186" s="29">
         <f t="shared" si="4"/>
         <v>1411399</v>
       </c>
-      <c r="D186" s="4">
+      <c r="D186">
         <f t="shared" si="5"/>
         <v>31709502</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="8">
+      <c r="A187" s="3">
+        <v>41426</v>
+      </c>
+      <c r="B187" s="8">
         <v>32300467</v>
       </c>
-      <c r="B187" s="3">
-        <v>41426</v>
-      </c>
       <c r="C187" s="29">
-        <f>D187</f>
-        <v>33337477.5</v>
-      </c>
-      <c r="D187" s="4">
+        <f t="shared" si="4"/>
+        <v>-229469</v>
+      </c>
+      <c r="D187">
         <f t="shared" si="5"/>
         <v>33337477.5</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="8">
+      <c r="A188" s="3">
+        <v>41456</v>
+      </c>
+      <c r="B188" s="8">
         <v>34145019</v>
-      </c>
-      <c r="B188" s="3">
-        <v>41456</v>
       </c>
       <c r="C188" s="29">
         <f t="shared" si="4"/>
         <v>1844552</v>
       </c>
-      <c r="D188" s="4">
+      <c r="D188">
         <f t="shared" si="5"/>
         <v>32768576</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="8">
+      <c r="A189" s="3">
+        <v>41487</v>
+      </c>
+      <c r="B189" s="8">
         <v>33236685</v>
-      </c>
-      <c r="B189" s="3">
-        <v>41487</v>
       </c>
       <c r="C189" s="29">
         <f t="shared" si="4"/>
         <v>-908334</v>
       </c>
-      <c r="D189" s="4">
+      <c r="D189">
         <f t="shared" si="5"/>
         <v>33534995</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="8">
+      <c r="A190" s="3">
+        <v>41518</v>
+      </c>
+      <c r="B190" s="8">
         <v>32924971</v>
-      </c>
-      <c r="B190" s="3">
-        <v>41518</v>
       </c>
       <c r="C190" s="29">
         <f t="shared" si="4"/>
         <v>-311714</v>
       </c>
-      <c r="D190" s="4">
+      <c r="D190">
         <f t="shared" si="5"/>
         <v>33484793.5</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="8">
+      <c r="A191" s="3">
+        <v>41548</v>
+      </c>
+      <c r="B191" s="8">
         <v>33732902</v>
-      </c>
-      <c r="B191" s="3">
-        <v>41548</v>
       </c>
       <c r="C191" s="29">
         <f t="shared" si="4"/>
         <v>807931</v>
       </c>
-      <c r="D191" s="4">
+      <c r="D191">
         <f t="shared" si="5"/>
         <v>32885183.5</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="8">
+      <c r="A192" s="3">
+        <v>41579</v>
+      </c>
+      <c r="B192" s="8">
         <v>32845396</v>
-      </c>
-      <c r="B192" s="3">
-        <v>41579</v>
       </c>
       <c r="C192" s="29">
         <f t="shared" si="4"/>
         <v>-887506</v>
       </c>
-      <c r="D192" s="4">
+      <c r="D192">
         <f t="shared" si="5"/>
         <v>33962067</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="8">
+      <c r="A193" s="3">
+        <v>41609</v>
+      </c>
+      <c r="B193" s="8">
         <v>34191232</v>
-      </c>
-      <c r="B193" s="3">
-        <v>41609</v>
       </c>
       <c r="C193" s="29">
         <f t="shared" si="4"/>
         <v>1345836</v>
       </c>
-      <c r="D193" s="4">
+      <c r="D193">
         <f t="shared" si="5"/>
         <v>33312852</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="8">
+      <c r="A194" s="3">
+        <v>41640</v>
+      </c>
+      <c r="B194" s="8">
         <v>33780308</v>
-      </c>
-      <c r="B194" s="3">
-        <v>41640</v>
       </c>
       <c r="C194" s="29">
         <f t="shared" si="4"/>
         <v>-410924</v>
       </c>
-      <c r="D194" s="4">
+      <c r="D194">
         <f t="shared" si="5"/>
         <v>32706390</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="8">
+      <c r="A195" s="3">
+        <v>41671</v>
+      </c>
+      <c r="B195" s="8">
         <v>31221548</v>
       </c>
-      <c r="B195" s="3">
-        <v>41671</v>
-      </c>
       <c r="C195" s="29">
-        <f>D195</f>
-        <v>33369522.5</v>
-      </c>
-      <c r="D195" s="4">
+        <f t="shared" si="4"/>
+        <v>-2558760</v>
+      </c>
+      <c r="D195">
         <f t="shared" si="5"/>
         <v>33369522.5</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="8">
+      <c r="A196" s="3">
+        <v>41699</v>
+      </c>
+      <c r="B196" s="8">
         <v>32958737</v>
       </c>
-      <c r="B196" s="3">
-        <v>41699</v>
-      </c>
       <c r="C196" s="29">
-        <f t="shared" ref="C196:C259" si="6">A196-A195</f>
+        <f t="shared" ref="C196:C259" si="6">B196-B195</f>
         <v>1737189</v>
       </c>
-      <c r="D196" s="4">
-        <f t="shared" ref="D196:D259" si="7">(A195+A197)/2</f>
+      <c r="D196">
+        <f t="shared" ref="D196:D259" si="7">(B195+B197)/2</f>
         <v>32305335</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="8">
+      <c r="A197" s="3">
+        <v>41730</v>
+      </c>
+      <c r="B197" s="8">
         <v>33389122</v>
-      </c>
-      <c r="B197" s="3">
-        <v>41730</v>
       </c>
       <c r="C197" s="29">
         <f t="shared" si="6"/>
         <v>430385</v>
       </c>
-      <c r="D197" s="4">
+      <c r="D197">
         <f t="shared" si="7"/>
         <v>33810996</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="8">
+      <c r="A198" s="3">
+        <v>41760</v>
+      </c>
+      <c r="B198" s="8">
         <v>34663255</v>
-      </c>
-      <c r="B198" s="3">
-        <v>41760</v>
       </c>
       <c r="C198" s="29">
         <f t="shared" si="6"/>
         <v>1274133</v>
       </c>
-      <c r="D198" s="4">
+      <c r="D198">
         <f t="shared" si="7"/>
         <v>33687146</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="8">
+      <c r="A199" s="3">
+        <v>41791</v>
+      </c>
+      <c r="B199" s="8">
         <v>33985170</v>
-      </c>
-      <c r="B199" s="3">
-        <v>41791</v>
       </c>
       <c r="C199" s="29">
         <f t="shared" si="6"/>
         <v>-678085</v>
       </c>
-      <c r="D199" s="4">
+      <c r="D199">
         <f t="shared" si="7"/>
         <v>34735776</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="8">
+      <c r="A200" s="3">
+        <v>41821</v>
+      </c>
+      <c r="B200" s="8">
         <v>34808297</v>
-      </c>
-      <c r="B200" s="3">
-        <v>41821</v>
       </c>
       <c r="C200" s="29">
         <f t="shared" si="6"/>
         <v>823127</v>
       </c>
-      <c r="D200" s="4">
+      <c r="D200">
         <f t="shared" si="7"/>
         <v>34755762.5</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="8">
+      <c r="A201" s="3">
+        <v>41852</v>
+      </c>
+      <c r="B201" s="8">
         <v>35526355</v>
-      </c>
-      <c r="B201" s="3">
-        <v>41852</v>
       </c>
       <c r="C201" s="29">
         <f t="shared" si="6"/>
         <v>718058</v>
       </c>
-      <c r="D201" s="4">
+      <c r="D201">
         <f t="shared" si="7"/>
         <v>34546337.5</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="8">
+      <c r="A202" s="3">
+        <v>41883</v>
+      </c>
+      <c r="B202" s="8">
         <v>34284378</v>
-      </c>
-      <c r="B202" s="3">
-        <v>41883</v>
       </c>
       <c r="C202" s="29">
         <f t="shared" si="6"/>
         <v>-1241977</v>
       </c>
-      <c r="D202" s="4">
+      <c r="D202">
         <f t="shared" si="7"/>
         <v>35176541</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" s="8">
+      <c r="A203" s="3">
+        <v>41913</v>
+      </c>
+      <c r="B203" s="8">
         <v>34826727</v>
-      </c>
-      <c r="B203" s="3">
-        <v>41913</v>
       </c>
       <c r="C203" s="29">
         <f t="shared" si="6"/>
         <v>542349</v>
       </c>
-      <c r="D203" s="4">
+      <c r="D203">
         <f t="shared" si="7"/>
         <v>34542367.5</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="8">
+      <c r="A204" s="3">
+        <v>41944</v>
+      </c>
+      <c r="B204" s="8">
         <v>34800357</v>
-      </c>
-      <c r="B204" s="3">
-        <v>41944</v>
       </c>
       <c r="C204" s="29">
         <f t="shared" si="6"/>
         <v>-26370</v>
       </c>
-      <c r="D204" s="4">
+      <c r="D204">
         <f t="shared" si="7"/>
         <v>35119333</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="8">
+      <c r="A205" s="3">
+        <v>41974</v>
+      </c>
+      <c r="B205" s="8">
         <v>35411939</v>
-      </c>
-      <c r="B205" s="3">
-        <v>41974</v>
       </c>
       <c r="C205" s="29">
         <f t="shared" si="6"/>
         <v>611582</v>
       </c>
-      <c r="D205" s="4">
+      <c r="D205">
         <f t="shared" si="7"/>
         <v>34943717</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="8">
+      <c r="A206" s="3">
+        <v>42005</v>
+      </c>
+      <c r="B206" s="8">
         <v>35087077</v>
-      </c>
-      <c r="B206" s="3">
-        <v>42005</v>
       </c>
       <c r="C206" s="29">
         <f t="shared" si="6"/>
         <v>-324862</v>
       </c>
-      <c r="D206" s="4">
+      <c r="D206">
         <f t="shared" si="7"/>
-        <v>35329144.75</v>
+        <v>35329230</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" s="8">
-        <f>D207</f>
-        <v>35246350.5</v>
-      </c>
-      <c r="B207" s="3">
+      <c r="A207" s="3">
         <v>42036</v>
       </c>
+      <c r="B207" s="8">
+        <v>35246521</v>
+      </c>
       <c r="C207" s="29">
-        <f>D207</f>
-        <v>35246350.5</v>
-      </c>
-      <c r="D207" s="4">
+        <f t="shared" si="6"/>
+        <v>159444</v>
+      </c>
+      <c r="D207">
         <f t="shared" si="7"/>
         <v>35246350.5</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" s="8">
+      <c r="A208" s="3">
+        <v>42064</v>
+      </c>
+      <c r="B208" s="8">
         <v>35405624</v>
-      </c>
-      <c r="B208" s="3">
-        <v>42064</v>
       </c>
       <c r="C208" s="29">
         <f t="shared" si="6"/>
-        <v>159273.5</v>
-      </c>
-      <c r="D208" s="4">
+        <v>159103</v>
+      </c>
+      <c r="D208">
         <f t="shared" si="7"/>
-        <v>34911252</v>
+        <v>34187889</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="8">
-        <f>D209</f>
-        <v>34576153.5</v>
-      </c>
-      <c r="B209" s="3">
+      <c r="A209" s="3">
         <v>42095</v>
+      </c>
+      <c r="B209" s="8">
+        <v>33129257</v>
       </c>
       <c r="C209" s="29">
         <f t="shared" si="6"/>
-        <v>-829470.5</v>
-      </c>
-      <c r="D209" s="4">
+        <v>-2276367</v>
+      </c>
+      <c r="D209">
         <f t="shared" si="7"/>
         <v>34576153.5</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="8">
+      <c r="A210" s="3">
+        <v>42125</v>
+      </c>
+      <c r="B210" s="8">
         <v>33746683</v>
-      </c>
-      <c r="B210" s="3">
-        <v>42125</v>
       </c>
       <c r="C210" s="29">
         <f t="shared" si="6"/>
-        <v>-829470.5</v>
-      </c>
-      <c r="D210" s="4">
+        <v>617426</v>
+      </c>
+      <c r="D210">
         <f t="shared" si="7"/>
-        <v>33600702.25</v>
+        <v>32877254</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="8">
+      <c r="A211" s="3">
+        <v>42156</v>
+      </c>
+      <c r="B211" s="8">
         <v>32625251</v>
-      </c>
-      <c r="B211" s="3">
-        <v>42156</v>
       </c>
       <c r="C211" s="29">
         <f t="shared" si="6"/>
         <v>-1121432</v>
       </c>
-      <c r="D211" s="4">
+      <c r="D211">
         <f t="shared" si="7"/>
         <v>33958523.5</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" s="8">
+      <c r="A212" s="3">
+        <v>42186</v>
+      </c>
+      <c r="B212" s="8">
         <v>34170364</v>
-      </c>
-      <c r="B212" s="3">
-        <v>42186</v>
       </c>
       <c r="C212" s="29">
         <f t="shared" si="6"/>
         <v>1545113</v>
       </c>
-      <c r="D212" s="4">
+      <c r="D212">
         <f t="shared" si="7"/>
         <v>33350350.5</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" s="8">
+      <c r="A213" s="3">
+        <v>42217</v>
+      </c>
+      <c r="B213" s="8">
         <v>34075450</v>
-      </c>
-      <c r="B213" s="3">
-        <v>42217</v>
       </c>
       <c r="C213" s="29">
         <f t="shared" si="6"/>
         <v>-94914</v>
       </c>
-      <c r="D213" s="4">
+      <c r="D213">
         <f t="shared" si="7"/>
         <v>33268825</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="8">
+      <c r="A214" s="3">
+        <v>42248</v>
+      </c>
+      <c r="B214" s="8">
         <v>32367286</v>
-      </c>
-      <c r="B214" s="3">
-        <v>42248</v>
       </c>
       <c r="C214" s="29">
         <f t="shared" si="6"/>
         <v>-1708164</v>
       </c>
-      <c r="D214" s="4">
+      <c r="D214">
         <f t="shared" si="7"/>
         <v>33397138.5</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="8">
+      <c r="A215" s="3">
+        <v>42278</v>
+      </c>
+      <c r="B215" s="8">
         <v>32718827</v>
-      </c>
-      <c r="B215" s="3">
-        <v>42278</v>
       </c>
       <c r="C215" s="29">
         <f t="shared" si="6"/>
         <v>351541</v>
       </c>
-      <c r="D215" s="4">
+      <c r="D215">
         <f t="shared" si="7"/>
         <v>31881671.5</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" s="8">
+      <c r="A216" s="3">
+        <v>42309</v>
+      </c>
+      <c r="B216" s="8">
         <v>31396057</v>
-      </c>
-      <c r="B216" s="3">
-        <v>42309</v>
       </c>
       <c r="C216" s="29">
         <f t="shared" si="6"/>
         <v>-1322770</v>
       </c>
-      <c r="D216" s="4">
+      <c r="D216">
         <f t="shared" si="7"/>
         <v>32262230</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A217" s="8">
+      <c r="A217" s="3">
+        <v>42339</v>
+      </c>
+      <c r="B217" s="8">
         <v>31805633</v>
-      </c>
-      <c r="B217" s="3">
-        <v>42339</v>
       </c>
       <c r="C217" s="29">
         <f t="shared" si="6"/>
         <v>409576</v>
       </c>
-      <c r="D217" s="4">
+      <c r="D217">
         <f t="shared" si="7"/>
-        <v>29648908</v>
+        <v>29530158.5</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A218" s="8">
-        <v>27901759</v>
-      </c>
-      <c r="B218" s="3">
+      <c r="A218" s="3">
         <v>42370</v>
       </c>
+      <c r="B218" s="8">
+        <v>27664260</v>
+      </c>
       <c r="C218" s="29">
-        <f>D218</f>
-        <v>27664259.5</v>
-      </c>
-      <c r="D218" s="4">
+        <f t="shared" si="6"/>
+        <v>-4141373</v>
+      </c>
+      <c r="D218">
         <f t="shared" si="7"/>
-        <v>27664259.5</v>
+        <v>28812576</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A219" s="8">
-        <v>23522886</v>
-      </c>
-      <c r="B219" s="3">
+      <c r="A219" s="3">
         <v>42401</v>
       </c>
+      <c r="B219" s="8">
+        <v>25819519</v>
+      </c>
       <c r="C219" s="29">
-        <f>D219</f>
-        <v>25938268</v>
-      </c>
-      <c r="D219" s="4">
+        <f t="shared" si="6"/>
+        <v>-1844741</v>
+      </c>
+      <c r="D219">
         <f t="shared" si="7"/>
-        <v>25938268</v>
+        <v>25819518.5</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A220" s="8">
+      <c r="A220" s="3">
+        <v>42430</v>
+      </c>
+      <c r="B220" s="8">
         <v>23974777</v>
-      </c>
-      <c r="B220" s="3">
-        <v>42430</v>
       </c>
       <c r="C220" s="29">
         <f t="shared" si="6"/>
-        <v>451891</v>
-      </c>
-      <c r="D220" s="4">
+        <v>-1844742</v>
+      </c>
+      <c r="D220">
         <f t="shared" si="7"/>
-        <v>23935953</v>
+        <v>25084269.5</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="8">
+      <c r="A221" s="3">
+        <v>42461</v>
+      </c>
+      <c r="B221" s="8">
         <v>24349020</v>
-      </c>
-      <c r="B221" s="3">
-        <v>42461</v>
       </c>
       <c r="C221" s="29">
         <f t="shared" si="6"/>
         <v>374243</v>
       </c>
-      <c r="D221" s="4">
+      <c r="D221">
         <f t="shared" si="7"/>
         <v>24971869.5</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="8">
+      <c r="A222" s="3">
+        <v>42491</v>
+      </c>
+      <c r="B222" s="8">
         <v>25968962</v>
-      </c>
-      <c r="B222" s="3">
-        <v>42491</v>
       </c>
       <c r="C222" s="29">
         <f t="shared" si="6"/>
         <v>1619942</v>
       </c>
-      <c r="D222" s="4">
+      <c r="D222">
         <f t="shared" si="7"/>
         <v>24917704</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="8">
+      <c r="A223" s="3">
+        <v>42522</v>
+      </c>
+      <c r="B223" s="8">
         <v>25486388</v>
-      </c>
-      <c r="B223" s="3">
-        <v>42522</v>
       </c>
       <c r="C223" s="29">
         <f t="shared" si="6"/>
         <v>-482574</v>
       </c>
-      <c r="D223" s="4">
+      <c r="D223">
         <f t="shared" si="7"/>
         <v>25711194</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A224" s="8">
+      <c r="A224" s="3">
+        <v>42552</v>
+      </c>
+      <c r="B224" s="8">
         <v>25453426</v>
-      </c>
-      <c r="B224" s="3">
-        <v>42552</v>
       </c>
       <c r="C224" s="29">
         <f t="shared" si="6"/>
         <v>-32962</v>
       </c>
-      <c r="D224" s="4">
+      <c r="D224">
         <f t="shared" si="7"/>
         <v>25549896</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A225" s="8">
+      <c r="A225" s="3">
+        <v>42583</v>
+      </c>
+      <c r="B225" s="8">
         <v>25613404</v>
-      </c>
-      <c r="B225" s="3">
-        <v>42583</v>
       </c>
       <c r="C225" s="29">
         <f t="shared" si="6"/>
         <v>159978</v>
       </c>
-      <c r="D225" s="4">
+      <c r="D225">
         <f t="shared" si="7"/>
         <v>25643870</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A226" s="8">
+      <c r="A226" s="3">
+        <v>42614</v>
+      </c>
+      <c r="B226" s="8">
         <v>25834314</v>
-      </c>
-      <c r="B226" s="3">
-        <v>42614</v>
       </c>
       <c r="C226" s="29">
         <f t="shared" si="6"/>
         <v>220910</v>
       </c>
-      <c r="D226" s="4">
+      <c r="D226">
         <f t="shared" si="7"/>
         <v>26267305</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A227" s="8">
+      <c r="A227" s="3">
+        <v>42644</v>
+      </c>
+      <c r="B227" s="8">
         <v>26921206</v>
-      </c>
-      <c r="B227" s="3">
-        <v>42644</v>
       </c>
       <c r="C227" s="29">
         <f t="shared" si="6"/>
         <v>1086892</v>
       </c>
-      <c r="D227" s="4">
+      <c r="D227">
         <f t="shared" si="7"/>
         <v>25839383</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="8">
+      <c r="A228" s="3">
+        <v>42675</v>
+      </c>
+      <c r="B228" s="8">
         <v>25844452</v>
-      </c>
-      <c r="B228" s="3">
-        <v>42675</v>
       </c>
       <c r="C228" s="29">
         <f t="shared" si="6"/>
         <v>-1076754</v>
       </c>
-      <c r="D228" s="4">
+      <c r="D228">
         <f t="shared" si="7"/>
         <v>26630120.5</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="8">
+      <c r="A229" s="3">
+        <v>42705</v>
+      </c>
+      <c r="B229" s="8">
         <v>26339035</v>
-      </c>
-      <c r="B229" s="3">
-        <v>42705</v>
       </c>
       <c r="C229" s="29">
         <f t="shared" si="6"/>
         <v>494583</v>
       </c>
-      <c r="D229" s="4">
+      <c r="D229">
         <f t="shared" si="7"/>
         <v>26160342</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A230" s="8">
+      <c r="A230" s="3">
+        <v>42736</v>
+      </c>
+      <c r="B230" s="8">
         <v>26476232</v>
-      </c>
-      <c r="B230" s="3">
-        <v>42736</v>
       </c>
       <c r="C230" s="29">
         <f t="shared" si="6"/>
         <v>137197</v>
       </c>
-      <c r="D230" s="4">
+      <c r="D230">
         <f t="shared" si="7"/>
-        <v>26342923.25</v>
+        <v>24941826</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" s="8">
-        <f>D231</f>
-        <v>26346811.5</v>
-      </c>
-      <c r="B231" s="3">
+      <c r="A231" s="3">
         <v>42767</v>
       </c>
+      <c r="B231" s="8">
+        <v>23544617</v>
+      </c>
       <c r="C231" s="29">
-        <f>D231</f>
-        <v>26346811.5</v>
-      </c>
-      <c r="D231" s="4">
+        <f t="shared" si="6"/>
+        <v>-2931615</v>
+      </c>
+      <c r="D231">
         <f t="shared" si="7"/>
         <v>26346811.5</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="8">
+      <c r="A232" s="3">
+        <v>42795</v>
+      </c>
+      <c r="B232" s="8">
         <v>26217391</v>
-      </c>
-      <c r="B232" s="3">
-        <v>42795</v>
       </c>
       <c r="C232" s="29">
         <f t="shared" si="6"/>
-        <v>-129420.5</v>
-      </c>
-      <c r="D232" s="4">
+        <v>2672774</v>
+      </c>
+      <c r="D232">
         <f t="shared" si="7"/>
-        <v>25839247.25</v>
+        <v>24438150</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A233" s="8">
+      <c r="A233" s="3">
+        <v>42826</v>
+      </c>
+      <c r="B233" s="8">
         <v>25331683</v>
-      </c>
-      <c r="B233" s="3">
-        <v>42826</v>
       </c>
       <c r="C233" s="29">
         <f t="shared" si="6"/>
         <v>-885708</v>
       </c>
-      <c r="D233" s="4">
+      <c r="D233">
         <f t="shared" si="7"/>
         <v>25512500</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A234" s="8">
+      <c r="A234" s="3">
+        <v>42856</v>
+      </c>
+      <c r="B234" s="8">
         <v>24807609</v>
-      </c>
-      <c r="B234" s="3">
-        <v>42856</v>
       </c>
       <c r="C234" s="29">
         <f t="shared" si="6"/>
         <v>-524074</v>
       </c>
-      <c r="D234" s="4">
+      <c r="D234">
         <f t="shared" si="7"/>
         <v>25172013.5</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A235" s="8">
+      <c r="A235" s="3">
+        <v>42887</v>
+      </c>
+      <c r="B235" s="8">
         <v>25012344</v>
-      </c>
-      <c r="B235" s="3">
-        <v>42887</v>
       </c>
       <c r="C235" s="29">
         <f t="shared" si="6"/>
         <v>204735</v>
       </c>
-      <c r="D235" s="4">
+      <c r="D235">
         <f t="shared" si="7"/>
         <v>24944055</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A236" s="8">
+      <c r="A236" s="3">
+        <v>42917</v>
+      </c>
+      <c r="B236" s="8">
         <v>25080501</v>
-      </c>
-      <c r="B236" s="3">
-        <v>42917</v>
       </c>
       <c r="C236" s="29">
         <f t="shared" si="6"/>
         <v>68157</v>
       </c>
-      <c r="D236" s="4">
+      <c r="D236">
         <f t="shared" si="7"/>
         <v>25489305</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A237" s="8">
+      <c r="A237" s="3">
+        <v>42948</v>
+      </c>
+      <c r="B237" s="8">
         <v>25966266</v>
-      </c>
-      <c r="B237" s="3">
-        <v>42948</v>
       </c>
       <c r="C237" s="29">
         <f t="shared" si="6"/>
         <v>885765</v>
       </c>
-      <c r="D237" s="4">
+      <c r="D237">
         <f t="shared" si="7"/>
         <v>25015666.5</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A238" s="8">
+      <c r="A238" s="3">
+        <v>42979</v>
+      </c>
+      <c r="B238" s="8">
         <v>24950832</v>
-      </c>
-      <c r="B238" s="3">
-        <v>42979</v>
       </c>
       <c r="C238" s="29">
         <f t="shared" si="6"/>
         <v>-1015434</v>
       </c>
-      <c r="D238" s="4">
+      <c r="D238">
         <f t="shared" si="7"/>
         <v>25868362.5</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A239" s="8">
+      <c r="A239" s="3">
+        <v>43009</v>
+      </c>
+      <c r="B239" s="8">
         <v>25770459</v>
-      </c>
-      <c r="B239" s="3">
-        <v>43009</v>
       </c>
       <c r="C239" s="29">
         <f t="shared" si="6"/>
         <v>819627</v>
       </c>
-      <c r="D239" s="4">
+      <c r="D239">
         <f t="shared" si="7"/>
         <v>25343557.5</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A240" s="8">
+      <c r="A240" s="3">
+        <v>43040</v>
+      </c>
+      <c r="B240" s="8">
         <v>25736283</v>
-      </c>
-      <c r="B240" s="3">
-        <v>43040</v>
       </c>
       <c r="C240" s="29">
         <f t="shared" si="6"/>
         <v>-34176</v>
       </c>
-      <c r="D240" s="4">
+      <c r="D240">
         <f t="shared" si="7"/>
         <v>26309968</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A241" s="8">
+      <c r="A241" s="3">
+        <v>43070</v>
+      </c>
+      <c r="B241" s="8">
         <v>26849477</v>
-      </c>
-      <c r="B241" s="3">
-        <v>43070</v>
       </c>
       <c r="C241" s="29">
         <f t="shared" si="6"/>
         <v>1113194</v>
       </c>
-      <c r="D241" s="4">
+      <c r="D241">
         <f t="shared" si="7"/>
         <v>26001635</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" s="8">
+      <c r="A242" s="3">
+        <v>43101</v>
+      </c>
+      <c r="B242" s="8">
         <v>26266987</v>
-      </c>
-      <c r="B242" s="3">
-        <v>43101</v>
       </c>
       <c r="C242" s="29">
         <f t="shared" si="6"/>
         <v>-582490</v>
       </c>
-      <c r="D242" s="4">
+      <c r="D242">
         <f t="shared" si="7"/>
         <v>25555601.5</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="8">
+      <c r="A243" s="3">
+        <v>43132</v>
+      </c>
+      <c r="B243" s="8">
         <v>24261726</v>
-      </c>
-      <c r="B243" s="3">
-        <v>43132</v>
       </c>
       <c r="C243" s="29">
         <f t="shared" si="6"/>
         <v>-2005261</v>
       </c>
-      <c r="D243" s="4">
+      <c r="D243">
         <f t="shared" si="7"/>
         <v>26392881</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A244" s="8">
+      <c r="A244" s="3">
+        <v>43160</v>
+      </c>
+      <c r="B244" s="8">
         <v>26518775</v>
-      </c>
-      <c r="B244" s="3">
-        <v>43160</v>
       </c>
       <c r="C244" s="29">
         <f t="shared" si="6"/>
         <v>2257049</v>
       </c>
-      <c r="D244" s="4">
+      <c r="D244">
         <f t="shared" si="7"/>
         <v>24701200</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A245" s="8">
+      <c r="A245" s="3">
+        <v>43191</v>
+      </c>
+      <c r="B245" s="8">
         <v>25140674</v>
-      </c>
-      <c r="B245" s="3">
-        <v>43191</v>
       </c>
       <c r="C245" s="29">
         <f t="shared" si="6"/>
         <v>-1378101</v>
       </c>
-      <c r="D245" s="4">
+      <c r="D245">
         <f t="shared" si="7"/>
         <v>26833025</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" s="8">
+      <c r="A246" s="3">
+        <v>43221</v>
+      </c>
+      <c r="B246" s="8">
         <v>27147275</v>
-      </c>
-      <c r="B246" s="3">
-        <v>43221</v>
       </c>
       <c r="C246" s="29">
         <f t="shared" si="6"/>
         <v>2006601</v>
       </c>
-      <c r="D246" s="4">
+      <c r="D246">
         <f t="shared" si="7"/>
         <v>25633589</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A247" s="8">
+      <c r="A247" s="3">
+        <v>43252</v>
+      </c>
+      <c r="B247" s="8">
         <v>26126504</v>
-      </c>
-      <c r="B247" s="3">
-        <v>43252</v>
       </c>
       <c r="C247" s="29">
         <f t="shared" si="6"/>
         <v>-1020771</v>
       </c>
-      <c r="D247" s="4">
+      <c r="D247">
         <f t="shared" si="7"/>
         <v>26884814.5</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" s="8">
+      <c r="A248" s="3">
+        <v>43282</v>
+      </c>
+      <c r="B248" s="8">
         <v>26622354</v>
-      </c>
-      <c r="B248" s="3">
-        <v>43282</v>
       </c>
       <c r="C248" s="29">
         <f t="shared" si="6"/>
         <v>495850</v>
       </c>
-      <c r="D248" s="4">
+      <c r="D248">
         <f t="shared" si="7"/>
         <v>26993568</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A249" s="8">
+      <c r="A249" s="3">
+        <v>43313</v>
+      </c>
+      <c r="B249" s="8">
         <v>27860632</v>
-      </c>
-      <c r="B249" s="3">
-        <v>43313</v>
       </c>
       <c r="C249" s="29">
         <f t="shared" si="6"/>
         <v>1238278</v>
       </c>
-      <c r="D249" s="4">
+      <c r="D249">
         <f t="shared" si="7"/>
         <v>26713213</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" s="8">
+      <c r="A250" s="3">
+        <v>43344</v>
+      </c>
+      <c r="B250" s="8">
         <v>26804072</v>
-      </c>
-      <c r="B250" s="3">
-        <v>43344</v>
       </c>
       <c r="C250" s="29">
         <f t="shared" si="6"/>
         <v>-1056560</v>
       </c>
-      <c r="D250" s="4">
+      <c r="D250">
         <f t="shared" si="7"/>
         <v>27740439</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" s="8">
+      <c r="A251" s="3">
+        <v>43374</v>
+      </c>
+      <c r="B251" s="8">
         <v>27620246</v>
-      </c>
-      <c r="B251" s="3">
-        <v>43374</v>
       </c>
       <c r="C251" s="29">
         <f t="shared" si="6"/>
         <v>816174</v>
       </c>
-      <c r="D251" s="4">
+      <c r="D251">
         <f t="shared" si="7"/>
         <v>26698829.5</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A252" s="8">
+      <c r="A252" s="3">
+        <v>43405</v>
+      </c>
+      <c r="B252" s="8">
         <v>26593587</v>
-      </c>
-      <c r="B252" s="3">
-        <v>43405</v>
       </c>
       <c r="C252" s="29">
         <f t="shared" si="6"/>
         <v>-1026659</v>
       </c>
-      <c r="D252" s="4">
+      <c r="D252">
         <f t="shared" si="7"/>
         <v>27340177.5</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="8">
+      <c r="A253" s="3">
+        <v>43435</v>
+      </c>
+      <c r="B253" s="8">
         <v>27060109</v>
-      </c>
-      <c r="B253" s="3">
-        <v>43435</v>
       </c>
       <c r="C253" s="29">
         <f t="shared" si="6"/>
         <v>466522</v>
       </c>
-      <c r="D253" s="4">
+      <c r="D253">
         <f t="shared" si="7"/>
         <v>26732451</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" s="8">
+      <c r="A254" s="3">
+        <v>43466</v>
+      </c>
+      <c r="B254" s="8">
         <v>26871315</v>
-      </c>
-      <c r="B254" s="3">
-        <v>43466</v>
       </c>
       <c r="C254" s="29">
         <f t="shared" si="6"/>
         <v>-188794</v>
       </c>
-      <c r="D254" s="4">
+      <c r="D254">
         <f t="shared" si="7"/>
         <v>25488421.5</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A255" s="8">
+      <c r="A255" s="3">
+        <v>43497</v>
+      </c>
+      <c r="B255" s="8">
         <v>23916734</v>
       </c>
-      <c r="B255" s="3">
-        <v>43497</v>
-      </c>
       <c r="C255" s="29">
-        <f>D255</f>
-        <v>26481534</v>
-      </c>
-      <c r="D255" s="4">
+        <f t="shared" si="6"/>
+        <v>-2954581</v>
+      </c>
+      <c r="D255">
         <f t="shared" si="7"/>
         <v>26481534</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A256" s="8">
+      <c r="A256" s="3">
+        <v>43525</v>
+      </c>
+      <c r="B256" s="8">
         <v>26091753</v>
-      </c>
-      <c r="B256" s="3">
-        <v>43525</v>
       </c>
       <c r="C256" s="29">
         <f t="shared" si="6"/>
         <v>2175019</v>
       </c>
-      <c r="D256" s="4">
+      <c r="D256">
         <f t="shared" si="7"/>
         <v>24516870.5</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A257" s="8">
+      <c r="A257" s="3">
+        <v>43556</v>
+      </c>
+      <c r="B257" s="8">
         <v>25117007</v>
-      </c>
-      <c r="B257" s="3">
-        <v>43556</v>
       </c>
       <c r="C257" s="29">
         <f t="shared" si="6"/>
         <v>-974746</v>
       </c>
-      <c r="D257" s="4">
+      <c r="D257">
         <f t="shared" si="7"/>
         <v>24731300.5</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A258" s="8">
+      <c r="A258" s="3">
+        <v>43586</v>
+      </c>
+      <c r="B258" s="8">
         <v>23370848</v>
-      </c>
-      <c r="B258" s="3">
-        <v>43586</v>
       </c>
       <c r="C258" s="29">
         <f t="shared" si="6"/>
         <v>-1746159</v>
       </c>
-      <c r="D258" s="4">
+      <c r="D258">
         <f t="shared" si="7"/>
         <v>24888949.5</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A259" s="8">
+      <c r="A259" s="3">
+        <v>43617</v>
+      </c>
+      <c r="B259" s="8">
         <v>24660892</v>
-      </c>
-      <c r="B259" s="3">
-        <v>43617</v>
       </c>
       <c r="C259" s="29">
         <f t="shared" si="6"/>
         <v>1290044</v>
       </c>
-      <c r="D259" s="4">
+      <c r="D259">
         <f t="shared" si="7"/>
         <v>24281057.5</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A260" s="8">
+      <c r="A260" s="3">
+        <v>43647</v>
+      </c>
+      <c r="B260" s="8">
         <v>25191267</v>
       </c>
-      <c r="B260" s="3">
-        <v>43647</v>
-      </c>
       <c r="C260" s="29">
-        <f t="shared" ref="C260:C323" si="8">A260-A259</f>
+        <f t="shared" ref="C260:C323" si="8">B260-B259</f>
         <v>530375</v>
       </c>
-      <c r="D260" s="4">
-        <f t="shared" ref="D260:D323" si="9">(A259+A261)/2</f>
+      <c r="D260">
+        <f t="shared" ref="D260:D323" si="9">(B259+B261)/2</f>
         <v>25153073</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A261" s="8">
+      <c r="A261" s="3">
+        <v>43678</v>
+      </c>
+      <c r="B261" s="8">
         <v>25645254</v>
-      </c>
-      <c r="B261" s="3">
-        <v>43678</v>
       </c>
       <c r="C261" s="29">
         <f t="shared" si="8"/>
         <v>453987</v>
       </c>
-      <c r="D261" s="4">
+      <c r="D261">
         <f t="shared" si="9"/>
         <v>25429492.5</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A262" s="8">
+      <c r="A262" s="3">
+        <v>43709</v>
+      </c>
+      <c r="B262" s="8">
         <v>25667718</v>
-      </c>
-      <c r="B262" s="3">
-        <v>43709</v>
       </c>
       <c r="C262" s="29">
         <f t="shared" si="8"/>
         <v>22464</v>
       </c>
-      <c r="D262" s="4">
+      <c r="D262">
         <f t="shared" si="9"/>
         <v>26260339</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" s="8">
+      <c r="A263" s="3">
+        <v>43739</v>
+      </c>
+      <c r="B263" s="8">
         <v>26875424</v>
-      </c>
-      <c r="B263" s="3">
-        <v>43739</v>
       </c>
       <c r="C263" s="29">
         <f t="shared" si="8"/>
         <v>1207706</v>
       </c>
-      <c r="D263" s="4">
+      <c r="D263">
         <f t="shared" si="9"/>
         <v>25872575</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A264" s="8">
+      <c r="A264" s="3">
+        <v>43770</v>
+      </c>
+      <c r="B264" s="8">
         <v>26077432</v>
-      </c>
-      <c r="B264" s="3">
-        <v>43770</v>
       </c>
       <c r="C264" s="29">
         <f t="shared" si="8"/>
         <v>-797992</v>
       </c>
-      <c r="D264" s="4">
+      <c r="D264">
         <f t="shared" si="9"/>
         <v>26816037</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A265" s="8">
+      <c r="A265" s="3">
+        <v>43800</v>
+      </c>
+      <c r="B265" s="8">
         <v>26756650</v>
-      </c>
-      <c r="B265" s="3">
-        <v>43800</v>
       </c>
       <c r="C265" s="29">
         <f t="shared" si="8"/>
         <v>679218</v>
       </c>
-      <c r="D265" s="4">
+      <c r="D265">
         <f t="shared" si="9"/>
         <v>26422138</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A266" s="8">
+      <c r="A266" s="3">
+        <v>43831</v>
+      </c>
+      <c r="B266" s="8">
         <v>26766844</v>
-      </c>
-      <c r="B266" s="3">
-        <v>43831</v>
       </c>
       <c r="C266" s="29">
         <f t="shared" si="8"/>
         <v>10194</v>
       </c>
-      <c r="D266" s="4">
+      <c r="D266">
         <f t="shared" si="9"/>
         <v>26074145</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A267" s="8">
+      <c r="A267" s="3">
+        <v>43862</v>
+      </c>
+      <c r="B267" s="8">
         <v>25391640</v>
-      </c>
-      <c r="B267" s="3">
-        <v>43862</v>
       </c>
       <c r="C267" s="29">
         <f t="shared" si="8"/>
         <v>-1375204</v>
       </c>
-      <c r="D267" s="4">
+      <c r="D267">
         <f t="shared" si="9"/>
         <v>26057962</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="8">
+      <c r="A268" s="3">
+        <v>43891</v>
+      </c>
+      <c r="B268" s="8">
         <v>25349080</v>
-      </c>
-      <c r="B268" s="3">
-        <v>43891</v>
       </c>
       <c r="C268" s="29">
         <f t="shared" si="8"/>
         <v>-42560</v>
       </c>
-      <c r="D268" s="4">
+      <c r="D268">
         <f t="shared" si="9"/>
-        <v>23165295.5</v>
+        <v>24172773.5</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" s="8">
-        <v>20938951</v>
-      </c>
-      <c r="B269" s="3">
+      <c r="A269" s="3">
         <v>43922</v>
       </c>
+      <c r="B269" s="8">
+        <v>22953907</v>
+      </c>
       <c r="C269" s="29">
-        <f>D269</f>
-        <v>22953907</v>
-      </c>
-      <c r="D269" s="4">
+        <f t="shared" si="8"/>
+        <v>-2395173</v>
+      </c>
+      <c r="D269">
         <f t="shared" si="9"/>
         <v>22953907</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A270" s="8">
+      <c r="A270" s="3">
+        <v>43952</v>
+      </c>
+      <c r="B270" s="8">
         <v>20558734</v>
-      </c>
-      <c r="B270" s="3">
-        <v>43952</v>
       </c>
       <c r="C270" s="29">
         <f t="shared" si="8"/>
-        <v>-380217</v>
-      </c>
-      <c r="D270" s="4">
+        <v>-2395173</v>
+      </c>
+      <c r="D270">
         <f t="shared" si="9"/>
-        <v>20558734</v>
+        <v>21566212</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A271" s="8">
+      <c r="A271" s="3">
+        <v>43983</v>
+      </c>
+      <c r="B271" s="8">
         <v>20178517</v>
-      </c>
-      <c r="B271" s="3">
-        <v>43983</v>
       </c>
       <c r="C271" s="29">
         <f t="shared" si="8"/>
         <v>-380217</v>
       </c>
-      <c r="D271" s="4">
+      <c r="D271">
         <f t="shared" si="9"/>
         <v>20971561</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A272" s="8">
+      <c r="A272" s="3">
+        <v>44013</v>
+      </c>
+      <c r="B272" s="8">
         <v>21384388</v>
-      </c>
-      <c r="B272" s="3">
-        <v>44013</v>
       </c>
       <c r="C272" s="29">
         <f t="shared" si="8"/>
         <v>1205871</v>
       </c>
-      <c r="D272" s="4">
+      <c r="D272">
         <f t="shared" si="9"/>
         <v>20959221.5</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="8">
+      <c r="A273" s="3">
+        <v>44044</v>
+      </c>
+      <c r="B273" s="8">
         <v>21739926</v>
-      </c>
-      <c r="B273" s="3">
-        <v>44044</v>
       </c>
       <c r="C273" s="29">
         <f t="shared" si="8"/>
         <v>355538</v>
       </c>
-      <c r="D273" s="4">
+      <c r="D273">
         <f t="shared" si="9"/>
         <v>21176775.5</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="8">
+      <c r="A274" s="3">
+        <v>44075</v>
+      </c>
+      <c r="B274" s="8">
         <v>20969163</v>
-      </c>
-      <c r="B274" s="3">
-        <v>44075</v>
       </c>
       <c r="C274" s="29">
         <f t="shared" si="8"/>
         <v>-770763</v>
       </c>
-      <c r="D274" s="4">
+      <c r="D274">
         <f t="shared" si="9"/>
         <v>21706343</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="8">
+      <c r="A275" s="3">
+        <v>44105</v>
+      </c>
+      <c r="B275" s="8">
         <v>21672760</v>
-      </c>
-      <c r="B275" s="3">
-        <v>44105</v>
       </c>
       <c r="C275" s="29">
         <f t="shared" si="8"/>
         <v>703597</v>
       </c>
-      <c r="D275" s="4">
+      <c r="D275">
         <f t="shared" si="9"/>
         <v>20926188</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="8">
+      <c r="A276" s="3">
+        <v>44136</v>
+      </c>
+      <c r="B276" s="8">
         <v>20883213</v>
-      </c>
-      <c r="B276" s="3">
-        <v>44136</v>
       </c>
       <c r="C276" s="29">
         <f t="shared" si="8"/>
         <v>-789547</v>
       </c>
-      <c r="D276" s="4">
+      <c r="D276">
         <f t="shared" si="9"/>
         <v>21654797</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="8">
+      <c r="A277" s="3">
+        <v>44166</v>
+      </c>
+      <c r="B277" s="8">
         <v>21636834</v>
-      </c>
-      <c r="B277" s="3">
-        <v>44166</v>
       </c>
       <c r="C277" s="29">
         <f t="shared" si="8"/>
         <v>753621</v>
       </c>
-      <c r="D277" s="4">
+      <c r="D277">
         <f t="shared" si="9"/>
         <v>20766111</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="8">
+      <c r="A278" s="3">
+        <v>44197</v>
+      </c>
+      <c r="B278" s="8">
         <v>20649009</v>
-      </c>
-      <c r="B278" s="3">
-        <v>44197</v>
       </c>
       <c r="C278" s="29">
         <f t="shared" si="8"/>
         <v>-987825</v>
       </c>
-      <c r="D278" s="4">
+      <c r="D278">
         <f t="shared" si="9"/>
-        <v>21207553.75</v>
+        <v>21207554</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="8">
-        <f>D279</f>
-        <v>20778273.5</v>
-      </c>
-      <c r="B279" s="3">
+      <c r="A279" s="3">
         <v>44228</v>
       </c>
+      <c r="B279" s="8">
+        <v>20778274</v>
+      </c>
       <c r="C279" s="29">
-        <f>D279</f>
-        <v>20778273.5</v>
-      </c>
-      <c r="D279" s="4">
+        <f t="shared" si="8"/>
+        <v>129265</v>
+      </c>
+      <c r="D279">
         <f t="shared" si="9"/>
         <v>20778273.5</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A280" s="8">
+      <c r="A280" s="3">
+        <v>44256</v>
+      </c>
+      <c r="B280" s="8">
         <v>20907538</v>
-      </c>
-      <c r="B280" s="3">
-        <v>44256</v>
       </c>
       <c r="C280" s="29">
         <f t="shared" si="8"/>
-        <v>129264.5</v>
-      </c>
-      <c r="D280" s="4">
+        <v>129264</v>
+      </c>
+      <c r="D280">
         <f t="shared" si="9"/>
-        <v>20641890.25</v>
+        <v>20641890.5</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="8">
+      <c r="A281" s="3">
+        <v>44287</v>
+      </c>
+      <c r="B281" s="8">
         <v>20505507</v>
-      </c>
-      <c r="B281" s="3">
-        <v>44287</v>
       </c>
       <c r="C281" s="29">
         <f t="shared" si="8"/>
         <v>-402031</v>
       </c>
-      <c r="D281" s="4">
+      <c r="D281">
         <f t="shared" si="9"/>
         <v>21115865</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="8">
+      <c r="A282" s="3">
+        <v>44317</v>
+      </c>
+      <c r="B282" s="8">
         <v>21324192</v>
-      </c>
-      <c r="B282" s="3">
-        <v>44317</v>
       </c>
       <c r="C282" s="29">
         <f t="shared" si="8"/>
         <v>818685</v>
       </c>
-      <c r="D282" s="4">
+      <c r="D282">
         <f t="shared" si="9"/>
         <v>20569953</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="8">
+      <c r="A283" s="3">
+        <v>44348</v>
+      </c>
+      <c r="B283" s="8">
         <v>20634399</v>
-      </c>
-      <c r="B283" s="3">
-        <v>44348</v>
       </c>
       <c r="C283" s="29">
         <f t="shared" si="8"/>
         <v>-689793</v>
       </c>
-      <c r="D283" s="4">
+      <c r="D283">
         <f t="shared" si="9"/>
         <v>21536533.5</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="8">
+      <c r="A284" s="3">
+        <v>44378</v>
+      </c>
+      <c r="B284" s="8">
         <v>21748875</v>
-      </c>
-      <c r="B284" s="3">
-        <v>44378</v>
       </c>
       <c r="C284" s="29">
         <f t="shared" si="8"/>
         <v>1114476</v>
       </c>
-      <c r="D284" s="4">
+      <c r="D284">
         <f t="shared" si="9"/>
         <v>21234447</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="8">
+      <c r="A285" s="3">
+        <v>44409</v>
+      </c>
+      <c r="B285" s="8">
         <v>21834495</v>
-      </c>
-      <c r="B285" s="3">
-        <v>44409</v>
       </c>
       <c r="C285" s="29">
         <f t="shared" si="8"/>
         <v>85620</v>
       </c>
-      <c r="D285" s="4">
+      <c r="D285">
         <f t="shared" si="9"/>
         <v>21521071</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="8">
+      <c r="A286" s="3">
+        <v>44440</v>
+      </c>
+      <c r="B286" s="8">
         <v>21293267</v>
-      </c>
-      <c r="B286" s="3">
-        <v>44440</v>
       </c>
       <c r="C286" s="29">
         <f t="shared" si="8"/>
         <v>-541228</v>
       </c>
-      <c r="D286" s="4">
+      <c r="D286">
         <f t="shared" si="9"/>
         <v>21964286.5</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="8">
+      <c r="A287" s="3">
+        <v>44470</v>
+      </c>
+      <c r="B287" s="8">
         <v>22094078</v>
-      </c>
-      <c r="B287" s="3">
-        <v>44470</v>
       </c>
       <c r="C287" s="29">
         <f t="shared" si="8"/>
         <v>800811</v>
       </c>
-      <c r="D287" s="4">
+      <c r="D287">
         <f t="shared" si="9"/>
         <v>21704592.5</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="8">
+      <c r="A288" s="3">
+        <v>44501</v>
+      </c>
+      <c r="B288" s="8">
         <v>22115918</v>
-      </c>
-      <c r="B288" s="3">
-        <v>44501</v>
       </c>
       <c r="C288" s="29">
         <f t="shared" si="8"/>
         <v>21840</v>
       </c>
-      <c r="D288" s="4">
+      <c r="D288">
         <f t="shared" si="9"/>
         <v>22754207</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="8">
+      <c r="A289" s="3">
+        <v>44531</v>
+      </c>
+      <c r="B289" s="8">
         <v>23414336</v>
-      </c>
-      <c r="B289" s="3">
-        <v>44531</v>
       </c>
       <c r="C289" s="29">
         <f t="shared" si="8"/>
         <v>1298418</v>
       </c>
-      <c r="D289" s="4">
+      <c r="D289">
         <f t="shared" si="9"/>
         <v>22639722.5</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="8">
+      <c r="A290" s="3">
+        <v>44562</v>
+      </c>
+      <c r="B290" s="8">
         <v>23163527</v>
-      </c>
-      <c r="B290" s="3">
-        <v>44562</v>
       </c>
       <c r="C290" s="29">
         <f t="shared" si="8"/>
         <v>-250809</v>
       </c>
-      <c r="D290" s="4">
+      <c r="D290">
         <f t="shared" si="9"/>
-        <v>22235883.5</v>
+        <v>23330485.5</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" s="8">
-        <v>21057431</v>
-      </c>
-      <c r="B291" s="3">
+      <c r="A291" s="3">
         <v>44593</v>
+      </c>
+      <c r="B291" s="8">
+        <v>23246635</v>
       </c>
       <c r="C291" s="29">
         <f t="shared" si="8"/>
-        <v>-2106096</v>
-      </c>
-      <c r="D291" s="4">
+        <v>83108</v>
+      </c>
+      <c r="D291">
         <f t="shared" si="9"/>
         <v>23246635</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="8">
+      <c r="A292" s="3">
+        <v>44621</v>
+      </c>
+      <c r="B292" s="8">
         <v>23329743</v>
-      </c>
-      <c r="B292" s="3">
-        <v>44621</v>
       </c>
       <c r="C292" s="29">
         <f t="shared" si="8"/>
-        <v>2272312</v>
-      </c>
-      <c r="D292" s="4">
+        <v>83108</v>
+      </c>
+      <c r="D292">
         <f t="shared" si="9"/>
-        <v>21591019.5</v>
+        <v>22685621.5</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="8">
+      <c r="A293" s="3">
+        <v>44652</v>
+      </c>
+      <c r="B293" s="8">
         <v>22124608</v>
-      </c>
-      <c r="B293" s="3">
-        <v>44652</v>
       </c>
       <c r="C293" s="29">
         <f t="shared" si="8"/>
         <v>-1205135</v>
       </c>
-      <c r="D293" s="4">
+      <c r="D293">
         <f t="shared" si="9"/>
         <v>23210734.5</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="8">
+      <c r="A294" s="3">
+        <v>44682</v>
+      </c>
+      <c r="B294" s="8">
         <v>23091726</v>
-      </c>
-      <c r="B294" s="3">
-        <v>44682</v>
       </c>
       <c r="C294" s="29">
         <f t="shared" si="8"/>
         <v>967118</v>
       </c>
-      <c r="D294" s="4">
+      <c r="D294">
         <f t="shared" si="9"/>
         <v>22681987.5</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="8">
+      <c r="A295" s="3">
+        <v>44713</v>
+      </c>
+      <c r="B295" s="8">
         <v>23239367</v>
-      </c>
-      <c r="B295" s="3">
-        <v>44713</v>
       </c>
       <c r="C295" s="29">
         <f t="shared" si="8"/>
         <v>147641</v>
       </c>
-      <c r="D295" s="4">
+      <c r="D295">
         <f t="shared" si="9"/>
         <v>23533736.5</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="8">
+      <c r="A296" s="3">
+        <v>44743</v>
+      </c>
+      <c r="B296" s="8">
         <v>23975747</v>
-      </c>
-      <c r="B296" s="3">
-        <v>44743</v>
       </c>
       <c r="C296" s="29">
         <f t="shared" si="8"/>
         <v>736380</v>
       </c>
-      <c r="D296" s="4">
+      <c r="D296">
         <f t="shared" si="9"/>
         <v>23681933</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="4">
+      <c r="A297" s="3">
+        <v>44774</v>
+      </c>
+      <c r="B297" s="4">
         <v>24124499</v>
-      </c>
-      <c r="B297" s="3">
-        <v>44774</v>
       </c>
       <c r="C297" s="29">
         <f t="shared" si="8"/>
         <v>148752</v>
       </c>
-      <c r="D297" s="4">
+      <c r="D297">
         <f t="shared" si="9"/>
         <v>24002145</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" s="8">
+      <c r="A298" s="3">
+        <v>44805</v>
+      </c>
+      <c r="B298" s="8">
         <v>24028543</v>
-      </c>
-      <c r="B298" s="3">
-        <v>44805</v>
       </c>
       <c r="C298" s="29">
         <f t="shared" si="8"/>
         <v>-95956</v>
       </c>
-      <c r="D298" s="4">
+      <c r="D298">
         <f t="shared" si="9"/>
         <v>24169007.5</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="8">
+      <c r="A299" s="3">
+        <v>44835</v>
+      </c>
+      <c r="B299" s="8">
         <v>24213516</v>
-      </c>
-      <c r="B299" s="3">
-        <v>44835</v>
       </c>
       <c r="C299" s="29">
         <f t="shared" si="8"/>
         <v>184973</v>
       </c>
-      <c r="D299" s="4">
+      <c r="D299">
         <f t="shared" si="9"/>
         <v>24086626</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" s="8">
+      <c r="A300" s="3">
+        <v>44866</v>
+      </c>
+      <c r="B300" s="8">
         <v>24144709</v>
-      </c>
-      <c r="B300" s="3">
-        <v>44866</v>
       </c>
       <c r="C300" s="29">
         <f t="shared" si="8"/>
         <v>-68807</v>
       </c>
-      <c r="D300" s="4">
+      <c r="D300">
         <f t="shared" si="9"/>
         <v>24272882</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" s="8">
+      <c r="A301" s="3">
+        <v>44896</v>
+      </c>
+      <c r="B301" s="8">
         <v>24332248</v>
-      </c>
-      <c r="B301" s="3">
-        <v>44896</v>
       </c>
       <c r="C301" s="29">
         <f t="shared" si="8"/>
         <v>187539</v>
       </c>
-      <c r="D301" s="4">
+      <c r="D301">
         <f t="shared" si="9"/>
         <v>24359981.5</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="8">
+      <c r="A302" s="3">
+        <v>44927</v>
+      </c>
+      <c r="B302" s="8">
         <v>24575254</v>
-      </c>
-      <c r="B302" s="3">
-        <v>44927</v>
       </c>
       <c r="C302" s="29">
         <f t="shared" si="8"/>
         <v>243006</v>
       </c>
-      <c r="D302" s="4">
+      <c r="D302">
         <f t="shared" si="9"/>
-        <v>23294107</v>
+        <v>24559501</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="8">
-        <v>22255966</v>
-      </c>
-      <c r="B303" s="3">
+      <c r="A303" s="3">
         <v>44958</v>
+      </c>
+      <c r="B303" s="8">
+        <v>24786754</v>
       </c>
       <c r="C303" s="29">
         <f t="shared" si="8"/>
-        <v>-2319288</v>
-      </c>
-      <c r="D303" s="4">
+        <v>211500</v>
+      </c>
+      <c r="D303">
         <f t="shared" si="9"/>
         <v>24786754</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" s="8">
+      <c r="A304" s="3">
+        <v>44986</v>
+      </c>
+      <c r="B304" s="8">
         <v>24998254</v>
-      </c>
-      <c r="B304" s="3">
-        <v>44986</v>
       </c>
       <c r="C304" s="29">
         <f t="shared" si="8"/>
-        <v>2742288</v>
-      </c>
-      <c r="D304" s="4">
+        <v>211500</v>
+      </c>
+      <c r="D304">
         <f t="shared" si="9"/>
-        <v>23091344.5</v>
+        <v>24356738.5</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A305" s="8">
+      <c r="A305" s="3">
+        <v>45017</v>
+      </c>
+      <c r="B305" s="8">
         <v>23926723</v>
-      </c>
-      <c r="B305" s="3">
-        <v>45017</v>
       </c>
       <c r="C305" s="29">
         <f t="shared" si="8"/>
         <v>-1071531</v>
       </c>
-      <c r="D305" s="4">
+      <c r="D305">
         <f t="shared" si="9"/>
         <v>25343583.5</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A306" s="8">
+      <c r="A306" s="3">
+        <v>45047</v>
+      </c>
+      <c r="B306" s="8">
         <v>25688913</v>
-      </c>
-      <c r="B306" s="3">
-        <v>45047</v>
       </c>
       <c r="C306" s="29">
         <f t="shared" si="8"/>
         <v>1762190</v>
       </c>
-      <c r="D306" s="4">
+      <c r="D306">
         <f t="shared" si="9"/>
-        <v>24684500.75</v>
+        <v>24684501</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A307" s="8">
-        <f>D307</f>
-        <v>25442278.5</v>
-      </c>
-      <c r="B307" s="3">
+      <c r="A307" s="3">
         <v>45078</v>
       </c>
+      <c r="B307" s="8">
+        <v>25442279</v>
+      </c>
       <c r="C307" s="29">
-        <f>D307</f>
-        <v>25442278.5</v>
-      </c>
-      <c r="D307" s="4">
+        <f t="shared" si="8"/>
+        <v>-246634</v>
+      </c>
+      <c r="D307">
         <f t="shared" si="9"/>
         <v>25442278.5</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A308" s="8">
+      <c r="A308" s="3">
+        <v>45108</v>
+      </c>
+      <c r="B308" s="8">
         <v>25195644</v>
-      </c>
-      <c r="B308" s="3">
-        <v>45108</v>
       </c>
       <c r="C308" s="29">
         <f t="shared" si="8"/>
-        <v>-246634.5</v>
-      </c>
-      <c r="D308" s="4">
+        <v>-246635</v>
+      </c>
+      <c r="D308">
         <f t="shared" si="9"/>
-        <v>25546063.75</v>
+        <v>25546064</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A309" s="8">
+      <c r="A309" s="3">
+        <v>45139</v>
+      </c>
+      <c r="B309" s="8">
         <v>25649849</v>
-      </c>
-      <c r="B309" s="3">
-        <v>45139</v>
       </c>
       <c r="C309" s="29">
         <f t="shared" si="8"/>
         <v>454205</v>
       </c>
-      <c r="D309" s="4">
+      <c r="D309">
         <f t="shared" si="9"/>
         <v>25088959</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A310" s="8">
+      <c r="A310" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B310" s="8">
         <v>24982274</v>
-      </c>
-      <c r="B310" s="3">
-        <v>45170</v>
       </c>
       <c r="C310" s="29">
         <f t="shared" si="8"/>
         <v>-667575</v>
       </c>
-      <c r="D310" s="4">
+      <c r="D310">
         <f t="shared" si="9"/>
         <v>26005757.5</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A311" s="8">
+      <c r="A311" s="3">
+        <v>45200</v>
+      </c>
+      <c r="B311" s="8">
         <v>26361666</v>
-      </c>
-      <c r="B311" s="3">
-        <v>45200</v>
       </c>
       <c r="C311" s="29">
         <f t="shared" si="8"/>
         <v>1379392</v>
       </c>
-      <c r="D311" s="4">
+      <c r="D311">
         <f t="shared" si="9"/>
         <v>25421976</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A312" s="8">
+      <c r="A312" s="3">
+        <v>45231</v>
+      </c>
+      <c r="B312" s="8">
         <v>25861678</v>
-      </c>
-      <c r="B312" s="3">
-        <v>45231</v>
       </c>
       <c r="C312" s="29">
         <f t="shared" si="8"/>
         <v>-499988</v>
       </c>
-      <c r="D312" s="4">
+      <c r="D312">
         <f t="shared" si="9"/>
         <v>26445922</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A313" s="8">
+      <c r="A313" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B313" s="8">
         <v>26530178</v>
-      </c>
-      <c r="B313" s="3">
-        <v>45261</v>
       </c>
       <c r="C313" s="29">
         <f t="shared" si="8"/>
         <v>668500</v>
       </c>
-      <c r="D313" s="4">
+      <c r="D313">
         <f t="shared" si="9"/>
         <v>25649002</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A314" s="8">
+      <c r="A314" s="3">
+        <v>45292</v>
+      </c>
+      <c r="B314" s="8">
         <v>25436326</v>
-      </c>
-      <c r="B314" s="3">
-        <v>45292</v>
       </c>
       <c r="C314" s="29">
         <f t="shared" si="8"/>
         <v>-1093852</v>
       </c>
-      <c r="D314" s="4">
+      <c r="D314">
         <f t="shared" si="9"/>
         <v>25708089.5</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A315" s="8">
+      <c r="A315" s="3">
+        <v>45323</v>
+      </c>
+      <c r="B315" s="8">
         <v>24886001</v>
-      </c>
-      <c r="B315" s="3">
-        <v>45323</v>
       </c>
       <c r="C315" s="29">
         <f t="shared" si="8"/>
         <v>-550325</v>
       </c>
-      <c r="D315" s="4">
+      <c r="D315">
         <f t="shared" si="9"/>
         <v>26153936</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A316" s="8">
+      <c r="A316" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B316" s="8">
         <v>26871546</v>
-      </c>
-      <c r="B316" s="3">
-        <v>45352</v>
       </c>
       <c r="C316" s="29">
         <f t="shared" si="8"/>
         <v>1985545</v>
       </c>
-      <c r="D316" s="4">
+      <c r="D316">
         <f t="shared" si="9"/>
         <v>24915434</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A317" s="8">
+      <c r="A317" s="3">
+        <v>45383</v>
+      </c>
+      <c r="B317" s="8">
         <v>24944867</v>
-      </c>
-      <c r="B317" s="3">
-        <v>45383</v>
       </c>
       <c r="C317" s="29">
         <f t="shared" si="8"/>
         <v>-1926679</v>
       </c>
-      <c r="D317" s="4">
+      <c r="D317">
         <f t="shared" si="9"/>
         <v>26349490.5</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A318" s="8">
+      <c r="A318" s="3">
+        <v>45413</v>
+      </c>
+      <c r="B318" s="8">
         <v>25827435</v>
-      </c>
-      <c r="B318" s="3">
-        <v>45413</v>
       </c>
       <c r="C318" s="29">
         <f t="shared" si="8"/>
         <v>882568</v>
       </c>
-      <c r="D318" s="4">
+      <c r="D318">
         <f t="shared" si="9"/>
         <v>25414548.5</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A319" s="8">
-        <f>D319</f>
+      <c r="A319" s="3">
+        <v>45444</v>
+      </c>
+      <c r="B319" s="8">
         <v>25884230</v>
       </c>
-      <c r="B319" s="3">
-        <v>45444</v>
-      </c>
       <c r="C319" s="29">
-        <f>D319</f>
-        <v>25884230</v>
-      </c>
-      <c r="D319" s="4">
+        <f t="shared" si="8"/>
+        <v>56795</v>
+      </c>
+      <c r="D319">
         <f t="shared" si="9"/>
         <v>25884230</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A320" s="8">
+      <c r="A320" s="3">
+        <v>45474</v>
+      </c>
+      <c r="B320" s="8">
         <v>25941025</v>
-      </c>
-      <c r="B320" s="3">
-        <v>45474</v>
       </c>
       <c r="C320" s="29">
         <f t="shared" si="8"/>
         <v>56795</v>
       </c>
-      <c r="D320" s="4">
+      <c r="D320">
         <f t="shared" si="9"/>
         <v>26417883.5</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A321" s="8">
+      <c r="A321" s="3">
+        <v>45505</v>
+      </c>
+      <c r="B321" s="8">
         <v>26951537</v>
-      </c>
-      <c r="B321" s="3">
-        <v>45505</v>
       </c>
       <c r="C321" s="29">
         <f t="shared" si="8"/>
         <v>1010512</v>
       </c>
-      <c r="D321" s="4">
+      <c r="D321">
         <f t="shared" si="9"/>
         <v>26140809.5</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A322" s="8">
+      <c r="A322" s="3">
+        <v>45536</v>
+      </c>
+      <c r="B322" s="8">
         <v>26340594</v>
-      </c>
-      <c r="B322" s="3">
-        <v>45536</v>
       </c>
       <c r="C322" s="29">
         <f t="shared" si="8"/>
         <v>-610943</v>
       </c>
-      <c r="D322" s="4">
+      <c r="D322">
         <f t="shared" si="9"/>
         <v>27304956</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A323" s="8">
+      <c r="A323" s="3">
+        <v>45566</v>
+      </c>
+      <c r="B323" s="8">
         <v>27658375</v>
-      </c>
-      <c r="B323" s="3">
-        <v>45566</v>
       </c>
       <c r="C323" s="29">
         <f t="shared" si="8"/>
         <v>1317781</v>
       </c>
-      <c r="D323" s="4">
+      <c r="D323">
         <f t="shared" si="9"/>
         <v>26681010</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A324" s="8">
+      <c r="A324" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B324" s="8">
         <v>27021426</v>
       </c>
-      <c r="B324" s="3">
-        <v>45597</v>
-      </c>
       <c r="C324" s="29">
-        <f t="shared" ref="C324:C344" si="10">A324-A323</f>
+        <f t="shared" ref="C324:C344" si="10">B324-B323</f>
         <v>-636949</v>
       </c>
-      <c r="D324" s="4">
-        <f t="shared" ref="D324:D344" si="11">(A323+A325)/2</f>
+      <c r="D324">
+        <f t="shared" ref="D324:D344" si="11">(B323+B325)/2</f>
         <v>27562162.5</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A325" s="8">
+      <c r="A325" s="3">
+        <v>45627</v>
+      </c>
+      <c r="B325" s="8">
         <v>27465950</v>
-      </c>
-      <c r="B325" s="3">
-        <v>45627</v>
       </c>
       <c r="C325" s="29">
         <f t="shared" si="10"/>
         <v>444524</v>
       </c>
-      <c r="D325" s="4">
+      <c r="D325">
         <f t="shared" si="11"/>
         <v>27167835</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A326" s="8">
+      <c r="A326" s="3">
+        <v>45658</v>
+      </c>
+      <c r="B326" s="8">
         <v>27314244</v>
-      </c>
-      <c r="B326" s="3">
-        <v>45658</v>
       </c>
       <c r="C326" s="29">
         <f t="shared" si="10"/>
         <v>-151706</v>
       </c>
-      <c r="D326" s="4">
+      <c r="D326">
         <f t="shared" si="11"/>
-        <v>27086483.75</v>
+        <v>27086484</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A327" s="8">
-        <f>D327</f>
-        <v>26707017.5</v>
-      </c>
-      <c r="B327" s="3">
+      <c r="A327" s="3">
         <v>45689</v>
       </c>
+      <c r="B327" s="8">
+        <v>26707018</v>
+      </c>
       <c r="C327" s="29">
-        <f>D327</f>
-        <v>26707017.5</v>
-      </c>
-      <c r="D327" s="4">
+        <f t="shared" si="10"/>
+        <v>-607226</v>
+      </c>
+      <c r="D327">
         <f t="shared" si="11"/>
         <v>26707017.5</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A328" s="8">
+      <c r="A328" s="3">
+        <v>45717</v>
+      </c>
+      <c r="B328" s="8">
         <v>26099791</v>
-      </c>
-      <c r="B328" s="3">
-        <v>45717</v>
       </c>
       <c r="C328" s="29">
         <f t="shared" si="10"/>
-        <v>-607226.5</v>
-      </c>
-      <c r="D328" s="4">
+        <v>-607227</v>
+      </c>
+      <c r="D328">
         <f t="shared" si="11"/>
-        <v>26629864.75</v>
+        <v>26629865</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A329" s="8">
+      <c r="A329" s="3">
+        <v>45748</v>
+      </c>
+      <c r="B329" s="8">
         <v>26552712</v>
-      </c>
-      <c r="B329" s="3">
-        <v>45748</v>
       </c>
       <c r="C329" s="29">
         <f t="shared" si="10"/>
         <v>452921</v>
       </c>
-      <c r="D329" s="4">
+      <c r="D329">
         <f t="shared" si="11"/>
         <v>26792695.5</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A330" s="8">
+      <c r="A330" s="3">
+        <v>45778</v>
+      </c>
+      <c r="B330" s="8">
         <v>27485600</v>
-      </c>
-      <c r="B330" s="3">
-        <v>45778</v>
       </c>
       <c r="C330" s="29">
         <f t="shared" si="10"/>
         <v>932888</v>
       </c>
-      <c r="D330" s="4">
+      <c r="D330">
         <f t="shared" si="11"/>
         <v>26416993.5</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A331" s="8">
+      <c r="A331" s="3">
+        <v>45809</v>
+      </c>
+      <c r="B331" s="8">
         <v>26281275</v>
-      </c>
-      <c r="B331" s="3">
-        <v>45809</v>
       </c>
       <c r="C331" s="29">
         <f t="shared" si="10"/>
         <v>-1204325</v>
       </c>
-      <c r="D331" s="4">
+      <c r="D331">
         <f t="shared" si="11"/>
         <v>27332785</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A332" s="8">
+      <c r="A332" s="3">
+        <v>45839</v>
+      </c>
+      <c r="B332" s="8">
         <v>27179970</v>
-      </c>
-      <c r="B332" s="3">
-        <v>45839</v>
       </c>
       <c r="C332" s="29">
         <f t="shared" si="10"/>
         <v>898695</v>
       </c>
-      <c r="D332" s="4">
+      <c r="D332">
         <f t="shared" si="11"/>
         <v>26710438</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A333" s="8">
+      <c r="A333" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B333" s="8">
         <v>27139601</v>
-      </c>
-      <c r="B333" s="3">
-        <v>45870</v>
       </c>
       <c r="C333" s="29">
         <f t="shared" si="10"/>
         <v>-40369</v>
       </c>
-      <c r="D333" s="4">
+      <c r="D333">
         <f t="shared" si="11"/>
         <v>26943559.5</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A334" s="8">
+      <c r="A334" s="3">
+        <v>45901</v>
+      </c>
+      <c r="B334" s="8">
         <v>26707149</v>
-      </c>
-      <c r="B334" s="3">
-        <v>45901</v>
       </c>
       <c r="C334" s="29">
         <f t="shared" si="10"/>
         <v>-432452</v>
       </c>
-      <c r="D334" s="4">
+      <c r="D334">
         <f t="shared" si="11"/>
         <v>27351030</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A335" s="8">
+      <c r="A335" s="3">
+        <v>45931</v>
+      </c>
+      <c r="B335" s="8">
         <v>27562459</v>
-      </c>
-      <c r="B335" s="3">
-        <v>45931</v>
       </c>
       <c r="C335" s="29">
         <f t="shared" si="10"/>
         <v>855310</v>
       </c>
-      <c r="D335" s="4">
+      <c r="D335">
         <f t="shared" si="11"/>
         <v>26605648</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A336" s="8">
+      <c r="A336" s="3">
+        <v>45962</v>
+      </c>
+      <c r="B336" s="8">
         <v>26504147</v>
-      </c>
-      <c r="B336" s="3">
-        <v>45962</v>
       </c>
       <c r="C336" s="29">
         <f t="shared" si="10"/>
         <v>-1058312</v>
       </c>
-      <c r="D336" s="4">
+      <c r="D336">
         <f t="shared" si="11"/>
         <v>27397004.5</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A337" s="8">
+      <c r="A337" s="3">
+        <v>45992</v>
+      </c>
+      <c r="B337" s="8">
         <v>27231550</v>
-      </c>
-      <c r="B337" s="3">
-        <v>45992</v>
       </c>
       <c r="C337" s="29">
         <f t="shared" si="10"/>
         <v>727403</v>
       </c>
-      <c r="D337" s="4">
+      <c r="D337">
         <f t="shared" si="11"/>
         <v>26362911.5</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A338" s="8">
+      <c r="A338" s="3">
+        <v>46023</v>
+      </c>
+      <c r="B338" s="8">
         <v>26221676</v>
-      </c>
-      <c r="B338" s="3">
-        <v>46023</v>
       </c>
       <c r="C338" s="29">
         <f t="shared" si="10"/>
         <v>-1009874</v>
       </c>
-      <c r="D338" s="4">
+      <c r="D338">
         <f t="shared" si="11"/>
-        <v>25704333</v>
+        <v>26963700</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A339" s="8">
-        <v>24177116</v>
-      </c>
-      <c r="B339" s="3">
+      <c r="A339" s="3">
         <v>46054</v>
+      </c>
+      <c r="B339" s="8">
+        <v>26695850</v>
       </c>
       <c r="C339" s="29">
         <f t="shared" si="10"/>
-        <v>-2044560</v>
-      </c>
-      <c r="D339" s="4">
+        <v>474174</v>
+      </c>
+      <c r="D339">
         <f t="shared" si="11"/>
         <v>26695850</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="8">
+      <c r="A340" s="3">
+        <v>46082</v>
+      </c>
+      <c r="B340" s="8">
         <v>27170024</v>
-      </c>
-      <c r="B340" s="3">
-        <v>46082</v>
       </c>
       <c r="C340" s="29">
         <f t="shared" si="10"/>
-        <v>2992908</v>
-      </c>
-      <c r="D340" s="4">
+        <v>474174</v>
+      </c>
+      <c r="D340">
         <f t="shared" si="11"/>
-        <v>25268993.5</v>
+        <v>26528360.5</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A341" s="8">
+      <c r="A341" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B341" s="8">
         <v>26360871</v>
-      </c>
-      <c r="B341" s="3">
-        <v>46113</v>
       </c>
       <c r="C341" s="29">
         <f t="shared" si="10"/>
         <v>-809153</v>
       </c>
-      <c r="D341" s="4">
+      <c r="D341">
         <f t="shared" si="11"/>
         <v>27239212.5</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A342" s="8">
+      <c r="A342" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B342" s="8">
         <v>27308401</v>
-      </c>
-      <c r="B342" s="3">
-        <v>46143</v>
       </c>
       <c r="C342" s="29">
         <f t="shared" si="10"/>
         <v>947530</v>
       </c>
-      <c r="D342" s="4">
+      <c r="D342">
         <f t="shared" si="11"/>
         <v>26371658</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A343" s="8">
+      <c r="A343" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B343" s="8">
         <v>26382445</v>
-      </c>
-      <c r="B343" s="3">
-        <v>46174</v>
       </c>
       <c r="C343" s="29">
         <f t="shared" si="10"/>
         <v>-925956</v>
       </c>
-      <c r="D343" s="4">
+      <c r="D343">
         <f t="shared" si="11"/>
         <v>27297946</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A344" s="8">
+      <c r="A344" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B344" s="8">
         <v>27287491</v>
-      </c>
-      <c r="B344" s="3">
-        <v>46204</v>
       </c>
       <c r="C344" s="29">
         <f t="shared" si="10"/>
         <v>905046</v>
       </c>
-      <c r="D344" s="4">
+      <c r="D344">
         <f t="shared" si="11"/>
         <v>13191222.5</v>
       </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C345" s="29"/>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C346" s="29"/>
+      <c r="D346" s="29"/>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C347" s="29"/>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C348" s="29"/>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C349" s="29"/>
+      <c r="D349" s="29"/>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C350" s="29"/>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C351" s="29"/>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C352" s="29"/>
+      <c r="D352" s="29"/>
+    </row>
+    <row r="353" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C353" s="29"/>
+    </row>
+    <row r="354" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C354" s="29"/>
+    </row>
+    <row r="355" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C355" s="29"/>
+      <c r="D355" s="29"/>
+    </row>
+    <row r="356" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C356" s="29"/>
+    </row>
+    <row r="357" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C357" s="29"/>
+    </row>
+    <row r="358" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C358" s="29"/>
+      <c r="D358" s="29"/>
+    </row>
+    <row r="359" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C359" s="29"/>
+    </row>
+    <row r="360" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C360" s="29"/>
+    </row>
+    <row r="361" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C361" s="29"/>
+      <c r="D361" s="29"/>
+    </row>
+    <row r="362" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C362" s="29"/>
+    </row>
+    <row r="363" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C363" s="29"/>
+    </row>
+    <row r="364" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C364" s="29"/>
+      <c r="D364" s="29"/>
+    </row>
+    <row r="365" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C365" s="29"/>
+    </row>
+    <row r="366" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C366" s="29"/>
+    </row>
+    <row r="367" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C367" s="29"/>
+      <c r="D367" s="29"/>
+    </row>
+    <row r="368" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C368" s="29"/>
+    </row>
+    <row r="369" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C369" s="29"/>
+    </row>
+    <row r="370" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C370" s="29"/>
+      <c r="D370" s="29"/>
+    </row>
+    <row r="371" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C371" s="29"/>
+    </row>
+    <row r="372" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C372" s="29"/>
+    </row>
+    <row r="373" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C373" s="29"/>
+      <c r="D373" s="29"/>
+    </row>
+    <row r="374" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C374" s="29"/>
+    </row>
+    <row r="375" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C375" s="29"/>
+    </row>
+    <row r="376" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C376" s="29"/>
+      <c r="D376" s="29"/>
+    </row>
+    <row r="377" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C377" s="29"/>
+    </row>
+    <row r="378" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C378" s="29"/>
+    </row>
+    <row r="379" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C379" s="29"/>
+      <c r="D379" s="29"/>
+    </row>
+    <row r="380" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C380" s="29"/>
+    </row>
+    <row r="381" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C381" s="29"/>
+    </row>
+    <row r="382" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C382" s="29"/>
+      <c r="D382" s="29"/>
+    </row>
+    <row r="383" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C383" s="29"/>
+    </row>
+    <row r="384" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C384" s="29"/>
+    </row>
+    <row r="385" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C385" s="29"/>
+      <c r="D385" s="29"/>
+    </row>
+    <row r="386" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C386" s="29"/>
+    </row>
+    <row r="387" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C387" s="29"/>
+    </row>
+    <row r="388" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C388" s="29"/>
+      <c r="D388" s="29"/>
+    </row>
+    <row r="389" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C389" s="29"/>
+    </row>
+    <row r="390" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C390" s="29"/>
+    </row>
+    <row r="391" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C391" s="29"/>
+      <c r="D391" s="29"/>
+    </row>
+    <row r="392" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C392" s="29"/>
+    </row>
+    <row r="393" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C393" s="29"/>
+    </row>
+    <row r="394" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C394" s="29"/>
+      <c r="D394" s="29"/>
+    </row>
+    <row r="395" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C395" s="29"/>
+    </row>
+    <row r="396" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C396" s="29"/>
+    </row>
+    <row r="397" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C397" s="29"/>
+      <c r="D397" s="29"/>
+    </row>
+    <row r="398" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C398" s="29"/>
+    </row>
+    <row r="399" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C399" s="29"/>
+    </row>
+    <row r="400" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C400" s="29"/>
+      <c r="D400" s="29"/>
+    </row>
+    <row r="401" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C401" s="29"/>
+    </row>
+    <row r="402" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C402" s="29"/>
+    </row>
+    <row r="403" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C403" s="29"/>
+      <c r="D403" s="29"/>
+    </row>
+    <row r="404" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C404" s="29"/>
+    </row>
+    <row r="405" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C405" s="29"/>
+    </row>
+    <row r="406" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C406" s="29"/>
+      <c r="D406" s="29"/>
+    </row>
+    <row r="407" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C407" s="29"/>
+    </row>
+    <row r="408" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C408" s="29"/>
+    </row>
+    <row r="409" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C409" s="29"/>
+      <c r="D409" s="29"/>
+    </row>
+    <row r="410" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C410" s="29"/>
+    </row>
+    <row r="411" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C411" s="29"/>
+    </row>
+    <row r="412" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C412" s="29"/>
+      <c r="D412" s="29"/>
+    </row>
+    <row r="413" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C413" s="29"/>
+    </row>
+    <row r="414" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C414" s="29"/>
+    </row>
+    <row r="415" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C415" s="29"/>
+      <c r="D415" s="29"/>
+    </row>
+    <row r="416" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C416" s="29"/>
+    </row>
+    <row r="417" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C417" s="29"/>
+    </row>
+    <row r="418" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C418" s="29"/>
+      <c r="D418" s="29"/>
+    </row>
+    <row r="419" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C419" s="29"/>
+    </row>
+    <row r="420" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C420" s="29"/>
+    </row>
+    <row r="421" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C421" s="29"/>
+      <c r="D421" s="29"/>
+    </row>
+    <row r="422" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C422" s="29"/>
+    </row>
+    <row r="423" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C423" s="29"/>
+    </row>
+    <row r="424" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C424" s="29"/>
+      <c r="D424" s="29"/>
+    </row>
+    <row r="425" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C425" s="29"/>
+    </row>
+    <row r="426" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C426" s="29"/>
+    </row>
+    <row r="427" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C427" s="29"/>
+      <c r="D427" s="29"/>
+    </row>
+    <row r="428" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C428" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Water Disposal History.xlsx
+++ b/Water Disposal History.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://etswdmail-my.sharepoint.com/personal/lfrideley_etswd_com/Documents/Documents/SARIMA Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="8_{9F342BE3-2F2B-4A33-86FA-5252C47A49C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0786317-38BA-4F04-AA8F-45FD45D92FC4}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{9F342BE3-2F2B-4A33-86FA-5252C47A49C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DFE77CB-E600-45AB-86F6-5ED5AF928D2C}"/>
   <bookViews>
     <workbookView xWindow="32175" yWindow="1530" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{85408E0C-C59E-4CA0-92DA-6AA07159AB49}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Month/ Year</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Total Water Volume 1</t>
+  </si>
+  <si>
+    <t>6-month moving average</t>
   </si>
 </sst>
 </file>
@@ -48315,14 +48318,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62516834-FDAB-45A0-893B-2B6358A8E52F}">
-  <dimension ref="A1:D428"/>
+  <dimension ref="A1:G428"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -48335,8 +48338,11 @@
       <c r="D1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>35796</v>
       </c>
@@ -48344,23 +48350,23 @@
         <v>33775964</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>35827</v>
       </c>
       <c r="B3" s="4">
-        <v>30600608</v>
+        <v>33721886</v>
       </c>
       <c r="C3" s="29">
         <f>B3-B2</f>
-        <v>-3175356</v>
+        <v>-54078</v>
       </c>
       <c r="D3">
         <f>(B2+B4)/2</f>
         <v>33721885.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>35855</v>
       </c>
@@ -48369,14 +48375,14 @@
       </c>
       <c r="C4" s="29">
         <f t="shared" ref="C4:C67" si="0">B4-B3</f>
-        <v>3067199</v>
+        <v>-54079</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:D67" si="1">(B3+B5)/2</f>
-        <v>31181405</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>32742044</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>35886</v>
       </c>
@@ -48392,7 +48398,7 @@
         <v>33083817.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>35916</v>
       </c>
@@ -48408,7 +48414,7 @@
         <v>31276953.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>35947</v>
       </c>
@@ -48424,7 +48430,7 @@
         <v>31833535.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>35977</v>
       </c>
@@ -48440,7 +48446,7 @@
         <v>30624828</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>36008</v>
       </c>
@@ -48456,7 +48462,7 @@
         <v>30066511.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>36039</v>
       </c>
@@ -48472,7 +48478,7 @@
         <v>30209072.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>36069</v>
       </c>
@@ -48488,7 +48494,7 @@
         <v>28534857.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>36100</v>
       </c>
@@ -48504,7 +48510,7 @@
         <v>28897874.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>36130</v>
       </c>
@@ -48520,7 +48526,7 @@
         <v>27652255.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>36161</v>
       </c>
@@ -48536,7 +48542,7 @@
         <v>27440151.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>36192</v>
       </c>
@@ -48552,7 +48558,7 @@
         <v>27044747.5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>36220</v>
       </c>
@@ -49797,7 +49803,7 @@
       </c>
       <c r="D93">
         <f t="shared" si="3"/>
-        <v>28343494.5</v>
+        <v>29846313.5</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -49805,11 +49811,11 @@
         <v>38596</v>
       </c>
       <c r="B94" s="8">
-        <v>27032542</v>
+        <v>30038180</v>
       </c>
       <c r="C94" s="29">
         <f t="shared" si="2"/>
-        <v>-3056873</v>
+        <v>-51235</v>
       </c>
       <c r="D94">
         <f t="shared" si="3"/>
@@ -49825,11 +49831,11 @@
       </c>
       <c r="C95" s="29">
         <f t="shared" si="2"/>
-        <v>2954403</v>
+        <v>-51235</v>
       </c>
       <c r="D95">
         <f t="shared" si="3"/>
-        <v>28201748.5</v>
+        <v>29704567.5</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -51413,7 +51419,7 @@
       </c>
       <c r="D194">
         <f t="shared" si="5"/>
-        <v>32706390</v>
+        <v>33780377.5</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -51421,11 +51427,11 @@
         <v>41671</v>
       </c>
       <c r="B195" s="8">
-        <v>31221548</v>
+        <v>33369523</v>
       </c>
       <c r="C195" s="29">
         <f t="shared" si="4"/>
-        <v>-2558760</v>
+        <v>-410785</v>
       </c>
       <c r="D195">
         <f t="shared" si="5"/>
@@ -51441,11 +51447,11 @@
       </c>
       <c r="C196" s="29">
         <f t="shared" ref="C196:C259" si="6">B196-B195</f>
-        <v>1737189</v>
+        <v>-410786</v>
       </c>
       <c r="D196">
         <f t="shared" ref="D196:D259" si="7">(B195+B197)/2</f>
-        <v>32305335</v>
+        <v>33379322.5</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -51637,7 +51643,7 @@
       </c>
       <c r="D208">
         <f t="shared" si="7"/>
-        <v>34187889</v>
+        <v>34911337.5</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -51645,11 +51651,11 @@
         <v>42095</v>
       </c>
       <c r="B209" s="8">
-        <v>33129257</v>
+        <v>34576154</v>
       </c>
       <c r="C209" s="29">
         <f t="shared" si="6"/>
-        <v>-2276367</v>
+        <v>-829470</v>
       </c>
       <c r="D209">
         <f t="shared" si="7"/>
@@ -51665,11 +51671,11 @@
       </c>
       <c r="C210" s="29">
         <f t="shared" si="6"/>
-        <v>617426</v>
+        <v>-829471</v>
       </c>
       <c r="D210">
         <f t="shared" si="7"/>
-        <v>32877254</v>
+        <v>33600702.5</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -54102,12 +54108,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1bd1721e-2220-476a-8a0c-275704810b64">
+      <UserInfo>
+        <DisplayName>Carter Matthews</DisplayName>
+        <AccountId>16</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d892915-ebce-4bfc-a614-64709b81479e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1bd1721e-2220-476a-8a0c-275704810b64" xsi:nil="true"/>
+    <AFEDate xmlns="3d892915-ebce-4bfc-a614-64709b81479e" xsi:nil="true"/>
+    <IntacctPROJNo_x002e_ xmlns="3d892915-ebce-4bfc-a614-64709b81479e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -54348,29 +54365,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1bd1721e-2220-476a-8a0c-275704810b64">
-      <UserInfo>
-        <DisplayName>Carter Matthews</DisplayName>
-        <AccountId>16</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d892915-ebce-4bfc-a614-64709b81479e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1bd1721e-2220-476a-8a0c-275704810b64" xsi:nil="true"/>
-    <AFEDate xmlns="3d892915-ebce-4bfc-a614-64709b81479e" xsi:nil="true"/>
-    <IntacctPROJNo_x002e_ xmlns="3d892915-ebce-4bfc-a614-64709b81479e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53071905-3A2E-49BD-A006-8C150C715FC8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA15176D-9C18-4E3E-9223-CD0FCCE499CD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3d892915-ebce-4bfc-a614-64709b81479e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="1bd1721e-2220-476a-8a0c-275704810b64"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -54395,18 +54410,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA15176D-9C18-4E3E-9223-CD0FCCE499CD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53071905-3A2E-49BD-A006-8C150C715FC8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3d892915-ebce-4bfc-a614-64709b81479e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="1bd1721e-2220-476a-8a0c-275704810b64"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>